--- a/projects/assets/political-text-analysis/ucdp-updated-through-august-2026.xlsx
+++ b/projects/assets/political-text-analysis/ucdp-updated-through-august-2026.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R6781fe9e31f44153"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US-involved events" sheetId="2" r:id="R1e8e921576804b21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Date comparison" sheetId="3" r:id="Rf13ac8a075dd4a33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R3bbb470cb55b4dc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="US-involved events" sheetId="2" r:id="Rf8a7cccb83ae4554"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Date comparison" sheetId="3" r:id="Re94d9a516c4c434a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -115,7 +115,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="59">
+  <x:cellXfs count="60">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -186,10 +186,11 @@
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
@@ -239,7 +240,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="USInvolvedIranEvents" displayName="USInvolvedIranEvents" ref="A1:AZ49" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="USInvolvedIranEvents" displayName="USInvolvedIranEvents" ref="A1:AZ50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="52">
     <x:tableColumn id="1" name="us_involvement"/>
     <x:tableColumn id="2" name="involvement_evidence"/>
@@ -499,7 +500,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>UCDP Iran Events with Explicit U.S. Involvement — 2026</x:v>
+        <x:v>UCDP Iran Events with Documented U.S. Involvement — 2026</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -529,12 +530,12 @@
         <x:v>Iran - Israel, United States of America</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="70" customHeight="1">
       <x:c r="A6" s="17" t="str">
         <x:v>Inclusion rule</x:v>
       </x:c>
       <x:c r="B6" s="18" t="str">
-        <x:v>UCDP source headline explicitly attributes the lethal event to the U.S. alone or to a joint U.S.-Israel action.</x:v>
+        <x:v>Documented U.S. or joint U.S.-Israel action, including lethal incidents reported during a U.S. operation. The rescue record documents operation context with the strike actor unspecified.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -542,16 +543,16 @@
         <x:v>Total included records</x:v>
       </x:c>
       <x:c r="B7" s="18" t="n">
-        <x:f>COUNTA('US-involved events'!C2:C49)</x:f>
-        <x:v>48</x:v>
+        <x:f>COUNTA('US-involved events'!C2:C50)</x:f>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="17" t="str">
-        <x:v>U.S.-only records</x:v>
+        <x:v>U.S.-attributed records</x:v>
       </x:c>
       <x:c r="B8" s="18" t="n">
-        <x:f>COUNTIF('US-involved events'!A2:A49,"US")</x:f>
+        <x:f>COUNTIF('US-involved events'!A2:A50,"US")</x:f>
         <x:v>22</x:v>
       </x:c>
     </x:row>
@@ -560,7 +561,7 @@
         <x:v>Joint U.S.-Israel records</x:v>
       </x:c>
       <x:c r="B9" s="18" t="n">
-        <x:f>COUNTIF('US-involved events'!A2:A49,"Joint US-Israel")</x:f>
+        <x:f>COUNTIF('US-involved events'!A2:A50,"Joint US-Israel")</x:f>
         <x:v>26</x:v>
       </x:c>
     </x:row>
@@ -572,6 +573,15 @@
         <x:v>2026-02-28 through 2026-08-30</x:v>
       </x:c>
     </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="35" t="str">
+        <x:v>U.S. operation-context records</x:v>
+      </x:c>
+      <x:c r="B11" s="34" t="n">
+        <x:f>COUNTIF('US-involved events'!A2:A50,"US operation context")</x:f>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
     <x:row r="12">
       <x:c r="A12" s="16" t="str">
         <x:v>Method note</x:v>
@@ -588,108 +598,124 @@
         <x:v>UCDP combines Israel and the United States on side_b for this conflict, so side_b alone cannot tell which country carried out a specific event.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="70" customHeight="1">
       <x:c r="A14" s="17" t="str">
         <x:v>How this file separates them</x:v>
       </x:c>
       <x:c r="B14" s="18" t="str">
-        <x:v>The new us_involvement field is based on explicit wording in UCDP's source_headline field.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
+        <x:v>Project us_involvement labels separate U.S. attribution, joint U.S.-Israel attribution, and U.S. operation context. Original UCDP actor fields are preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="70" customHeight="1">
       <x:c r="A15" s="17" t="str">
         <x:v>Excluded records</x:v>
       </x:c>
       <x:c r="B15" s="18" t="str">
-        <x:v>Israel-only records and ambiguous records were excluded when the headline did not explicitly connect the event to U.S. action.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>31 records are withheld because the reviewed evidence does not establish a U.S. role. They are not proven Israel-only. Current reasons are documented in the portfolio source viewer.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="70" customHeight="1">
       <x:c r="A16" s="17" t="str">
         <x:v>Use for Truth Social analysis</x:v>
       </x:c>
       <x:c r="B16" s="18" t="str">
-        <x:v>These are event records with explicit U.S. involvement that can be used as dated anchors around which to examine Trump's Iran-related Truth Social posts.</x:v>
+        <x:v>These selected records provide calendar-date anchors for examining Trump’s Iran-related posts. Multiple records on one start date share a single window.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="35" customHeight="1">
-      <x:c r="A19" s="40" t="str">
+      <x:c r="A19" s="41" t="str">
         <x:v>Workbook version</x:v>
       </x:c>
-      <x:c r="B19" s="39" t="str">
+      <x:c r="B19" s="40" t="str">
         <x:v>Updated reviewed extract through August 2026</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="35" customHeight="1">
-      <x:c r="A20" s="40" t="str">
+      <x:c r="A20" s="41" t="str">
         <x:v>Highlighted dates</x:v>
       </x:c>
-      <x:c r="B20" s="41" t="str">
+      <x:c r="B20" s="42" t="str">
         <x:v>Yellow: 26 original selected dates. Green: August 30 added. Gray: July 30 restored with no matched posts.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="35" customHeight="1">
-      <x:c r="A21" s="40" t="str">
+      <x:c r="A21" s="41" t="str">
         <x:v>Original extract</x:v>
       </x:c>
-      <x:c r="B21" s="39" t="str">
+      <x:c r="B21" s="40" t="str">
         <x:v>47 records across 27 event start dates; 26 dates used in the original post comparison.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="35" customHeight="1">
-      <x:c r="A22" s="40" t="str">
+      <x:c r="A22" s="41" t="str">
         <x:v>Current extract</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="str">
-        <x:v>48 records across 28 event start dates; 27 dates have any matched posts.</x:v>
+      <x:c r="B22" s="40" t="str">
+        <x:v>49 records across 28 event start dates; 27 dates have any matched posts.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="35" customHeight="1">
-      <x:c r="A23" s="40" t="str">
+      <x:c r="A23" s="41" t="str">
         <x:v>Color meaning</x:v>
       </x:c>
-      <x:c r="B23" s="39" t="str">
+      <x:c r="B23" s="40" t="str">
         <x:v>Highlighted date_start marks the analysis anchor. date_end retains the source interval and is not a separate selected date.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="35" customHeight="1">
-      <x:c r="A24" s="40" t="str">
+      <x:c r="A24" s="41" t="str">
         <x:v>Date detail</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="str">
+      <x:c r="B24" s="40" t="str">
         <x:v>See Date comparison for event IDs, selection status, and original/current matched-post counts.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="35" customHeight="1">
-      <x:c r="A25" s="40" t="str">
+      <x:c r="A25" s="41" t="str">
         <x:v>Original source</x:v>
       </x:c>
-      <x:c r="B25" s="39" t="str">
+      <x:c r="B25" s="40" t="str">
         <x:v>https://github.com/StrokeOfLuck/trump-iran-rhetoric-analysis/blob/main/data/UCDP_Iran_US_or_Joint_US_Involvement_2026_through_July.xlsx</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="35" customHeight="1">
-      <x:c r="A26" s="40" t="str">
+      <x:c r="A26" s="41" t="str">
         <x:v>Official source</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="str">
+      <x:c r="B26" s="40" t="str">
         <x:v>https://ucdp.uu.se/downloads/</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="35" customHeight="1">
-      <x:c r="A27" s="40" t="str">
+      <x:c r="A27" s="41" t="str">
         <x:v>Candidate versions</x:v>
       </x:c>
-      <x:c r="B27" s="39" t="str">
+      <x:c r="B27" s="40" t="str">
         <x:v>January–June 26.01.26.06; July 26.0.7; August 26.0.8</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="35" customHeight="1">
-      <x:c r="A28" s="40" t="str">
+      <x:c r="A28" s="41" t="str">
         <x:v>Data caution</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="str">
+      <x:c r="B28" s="40" t="str">
         <x:v>Candidate records are provisional. UCDP 625182 has low=best=2417 and high=2401 in the official source; values are preserved.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="75" customHeight="1">
+      <x:c r="A29" s="41" t="str">
+        <x:v>Selection correction</x:v>
+      </x:c>
+      <x:c r="B29" s="40" t="str">
+        <x:v>Added UCDP 629301 on April 5: five reported deaths during the U.S. pilot-rescue operation. Operation context is documented; the strike actor is unspecified.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="75" customHeight="1">
+      <x:c r="A30" s="41" t="str">
+        <x:v>Selection evidence</x:v>
+      </x:c>
+      <x:c r="B30" s="40" t="str">
+        <x:v>https://www.thedailystar.net/news/world/us-israel-war-iran/news/five-killed-iran-strikes-during-us-pilot-rescue-iranian-media-4144001</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -994,7 +1020,7 @@
       <x:c r="AN2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO2" s="34" t="d">
+      <x:c r="AO2" s="36" t="d">
         <x:v>2026-02-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP2" s="30" t="d">
@@ -1152,7 +1178,7 @@
       <x:c r="AN3" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO3" s="34" t="d">
+      <x:c r="AO3" s="36" t="d">
         <x:v>2026-02-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP3" s="30" t="d">
@@ -1302,7 +1328,7 @@
       <x:c r="AN4" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AO4" s="34" t="d">
+      <x:c r="AO4" s="36" t="d">
         <x:v>2026-02-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP4" s="30" t="d">
@@ -1462,7 +1488,7 @@
       <x:c r="AN5" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AO5" s="34" t="d">
+      <x:c r="AO5" s="36" t="d">
         <x:v>2026-02-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP5" s="30" t="d">
@@ -1614,7 +1640,7 @@
       <x:c r="AN6" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AO6" s="34" t="d">
+      <x:c r="AO6" s="36" t="d">
         <x:v>2026-02-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP6" s="30" t="d">
@@ -1766,7 +1792,7 @@
       <x:c r="AN7" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AO7" s="34" t="d">
+      <x:c r="AO7" s="36" t="d">
         <x:v>2026-02-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP7" s="30" t="d">
@@ -1920,7 +1946,7 @@
       <x:c r="AN8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="AO8" s="34" t="d">
+      <x:c r="AO8" s="36" t="d">
         <x:v>2026-02-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP8" s="30" t="d">
@@ -2068,7 +2094,7 @@
       <x:c r="AN9" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO9" s="34" t="d">
+      <x:c r="AO9" s="36" t="d">
         <x:v>2026-03-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP9" s="30" t="d">
@@ -2222,7 +2248,7 @@
       <x:c r="AN10" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO10" s="34" t="d">
+      <x:c r="AO10" s="36" t="d">
         <x:v>2026-03-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP10" s="30" t="d">
@@ -2374,7 +2400,7 @@
       <x:c r="AN11" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO11" s="34" t="d">
+      <x:c r="AO11" s="36" t="d">
         <x:v>2026-03-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP11" s="30" t="d">
@@ -2528,7 +2554,7 @@
       <x:c r="AN12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO12" s="34" t="d">
+      <x:c r="AO12" s="36" t="d">
         <x:v>2026-03-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP12" s="30" t="d">
@@ -2682,7 +2708,7 @@
       <x:c r="AN13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO13" s="34" t="d">
+      <x:c r="AO13" s="36" t="d">
         <x:v>2026-03-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP13" s="30" t="d">
@@ -2836,7 +2862,7 @@
       <x:c r="AN14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO14" s="34" t="d">
+      <x:c r="AO14" s="36" t="d">
         <x:v>2026-03-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP14" s="30" t="d">
@@ -2990,7 +3016,7 @@
       <x:c r="AN15" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO15" s="34" t="d">
+      <x:c r="AO15" s="36" t="d">
         <x:v>2026-03-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP15" s="30" t="d">
@@ -3144,7 +3170,7 @@
       <x:c r="AN16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO16" s="34" t="d">
+      <x:c r="AO16" s="36" t="d">
         <x:v>2026-03-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP16" s="30" t="d">
@@ -3298,7 +3324,7 @@
       <x:c r="AN17" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO17" s="34" t="d">
+      <x:c r="AO17" s="36" t="d">
         <x:v>2026-04-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP17" s="30" t="d">
@@ -3454,7 +3480,7 @@
       <x:c r="AN18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO18" s="34" t="d">
+      <x:c r="AO18" s="36" t="d">
         <x:v>2026-04-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP18" s="30" t="d">
@@ -3608,7 +3634,7 @@
       <x:c r="AN19" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO19" s="34" t="d">
+      <x:c r="AO19" s="36" t="d">
         <x:v>2026-04-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP19" s="30" t="d">
@@ -3762,7 +3788,7 @@
       <x:c r="AN20" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO20" s="34" t="d">
+      <x:c r="AO20" s="36" t="d">
         <x:v>2026-04-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP20" s="30" t="d">
@@ -3799,16 +3825,16 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="18" t="str">
-        <x:v>Joint US-Israel</x:v>
+        <x:v>US operation context</x:v>
       </x:c>
       <x:c r="B21" s="18" t="str">
-        <x:v>US-Israeli strikes kill five Guards members in northwest Iran: state media</x:v>
+        <x:v>Five killed in Iran in strikes during US pilot rescue: Iranian media</x:v>
       </x:c>
       <x:c r="C21" t="n">
-        <x:v>629302</x:v>
+        <x:v>629301</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>IRN-2026-1-18868-84</x:v>
+        <x:v>IRN-2026-1-18868-83</x:v>
       </x:c>
       <x:c r="E21" t="n">
         <x:v>2026</x:v>
@@ -3817,7 +3843,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G21" t="str">
-        <x:v>Check geography</x:v>
+        <x:v>Check deaths</x:v>
       </x:c>
       <x:c r="H21" t="n">
         <x:v>1</x:v>
@@ -3860,7 +3886,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V21" t="str">
-        <x:v>"Agence France Presse,2026-04-05,US-Israeli strikes kill five Guards members in northwest Iran: state media"</x:v>
+        <x:v>"Agence France Presse,2026-04-05,Five killed in Iran in strikes during US pilot rescue: Iranian media"</x:v>
       </x:c>
       <x:c r="W21" t="str">
         <x:v>Agence France Presse</x:v>
@@ -3869,35 +3895,37 @@
         <x:v>2026-04-05</x:v>
       </x:c>
       <x:c r="Y21" t="str">
-        <x:v>US-Israeli strikes kill five Guards members in northwest Iran: state media</x:v>
+        <x:v>Five killed in Iran in strikes during US pilot rescue: Iranian media</x:v>
       </x:c>
       <x:c r="Z21" t="str">
-        <x:v>Iran's official IRNA news agency</x:v>
+        <x:v>provincial official Iraj Kazemijou</x:v>
       </x:c>
       <x:c r="AA21" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AB21" t="str">
-        <x:v>Ardebil province</x:v>
+        <x:v>Boyer-Ahmad county</x:v>
       </x:c>
       <x:c r="AC21" t="str">
-        <x:v>Moghan Plain</x:v>
+        <x:v>"Kouh-e Siah area"</x:v>
       </x:c>
       <x:c r="AD21" t="str">
-        <x:v>Ardebil province</x:v>
-      </x:c>
-      <x:c r="AE21"/>
+        <x:v>Kohgiluyeh and Buyer Ahmad province</x:v>
+      </x:c>
+      <x:c r="AE21" t="str">
+        <x:v>Boyer-Ahmad county</x:v>
+      </x:c>
       <x:c r="AF21" t="n">
-        <x:v>38.2514</x:v>
+        <x:v>30.875</x:v>
       </x:c>
       <x:c r="AG21" t="n">
-        <x:v>48.2973</x:v>
+        <x:v>51.13333</x:v>
       </x:c>
       <x:c r="AH21" t="str">
-        <x:v>POINT (48.2973 38.2514)</x:v>
+        <x:v>POINT (51.13333 30.875)</x:v>
       </x:c>
       <x:c r="AI21" t="n">
-        <x:v>184777</x:v>
+        <x:v>173983</x:v>
       </x:c>
       <x:c r="AJ21" t="str">
         <x:v>Iran</x:v>
@@ -3914,23 +3942,23 @@
       <x:c r="AN21" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO21" s="34" t="d">
+      <x:c r="AO21" s="36" t="d">
         <x:v>2026-04-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP21" s="30" t="d">
         <x:v>2026-04-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AT21" t="n">
         <x:v>5</x:v>
-      </x:c>
-      <x:c r="AR21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT21" t="n">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="AU21" t="n">
         <x:v>5</x:v>
@@ -3954,13 +3982,13 @@
         <x:v>Joint US-Israel</x:v>
       </x:c>
       <x:c r="B22" s="18" t="str">
-        <x:v>US-Israeli strikes kill Iran Guards intelligence chief: Guards</x:v>
+        <x:v>US-Israeli strikes kill five Guards members in northwest Iran: state media</x:v>
       </x:c>
       <x:c r="C22" t="n">
-        <x:v>629305</x:v>
+        <x:v>629302</x:v>
       </x:c>
       <x:c r="D22" t="str">
-        <x:v>IRN-2026-1-18868-87</x:v>
+        <x:v>IRN-2026-1-18868-84</x:v>
       </x:c>
       <x:c r="E22" t="n">
         <x:v>2026</x:v>
@@ -3969,7 +3997,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G22" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Check geography</x:v>
       </x:c>
       <x:c r="H22" t="n">
         <x:v>1</x:v>
@@ -4012,46 +4040,44 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V22" t="str">
-        <x:v>"Agence France Presse,2026-04-06,US-Israeli strikes kill Iran Guards intelligence chief: Guards"</x:v>
+        <x:v>"Agence France Presse,2026-04-05,US-Israeli strikes kill five Guards members in northwest Iran: state media"</x:v>
       </x:c>
       <x:c r="W22" t="str">
         <x:v>Agence France Presse</x:v>
       </x:c>
       <x:c r="X22" t="str">
-        <x:v>2026-04-06</x:v>
+        <x:v>2026-04-05</x:v>
       </x:c>
       <x:c r="Y22" t="str">
-        <x:v>US-Israeli strikes kill Iran Guards intelligence chief: Guards</x:v>
+        <x:v>US-Israeli strikes kill five Guards members in northwest Iran: state media</x:v>
       </x:c>
       <x:c r="Z22" t="str">
-        <x:v>IRGC</x:v>
+        <x:v>Iran's official IRNA news agency</x:v>
       </x:c>
       <x:c r="AA22" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB22" t="str">
-        <x:v>Tehran city</x:v>
+        <x:v>Ardebil province</x:v>
       </x:c>
       <x:c r="AC22" t="str">
-        <x:v>Tehran</x:v>
+        <x:v>Moghan Plain</x:v>
       </x:c>
       <x:c r="AD22" t="str">
-        <x:v>Tehran province</x:v>
-      </x:c>
-      <x:c r="AE22" t="str">
-        <x:v>Tehran county</x:v>
-      </x:c>
+        <x:v>Ardebil province</x:v>
+      </x:c>
+      <x:c r="AE22"/>
       <x:c r="AF22" t="n">
-        <x:v>35.696111</x:v>
+        <x:v>38.2514</x:v>
       </x:c>
       <x:c r="AG22" t="n">
-        <x:v>51.423056</x:v>
+        <x:v>48.2973</x:v>
       </x:c>
       <x:c r="AH22" t="str">
-        <x:v>POINT (51.423056 35.696111)</x:v>
+        <x:v>POINT (48.2973 38.2514)</x:v>
       </x:c>
       <x:c r="AI22" t="n">
-        <x:v>181183</x:v>
+        <x:v>184777</x:v>
       </x:c>
       <x:c r="AJ22" t="str">
         <x:v>Iran</x:v>
@@ -4068,14 +4094,14 @@
       <x:c r="AN22" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO22" s="34" t="d">
-        <x:v>2026-04-06T00:00:00.000Z</x:v>
+      <x:c r="AO22" s="36" t="d">
+        <x:v>2026-04-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP22" s="30" t="d">
-        <x:v>2026-04-06T00:00:00.000Z</x:v>
+        <x:v>2026-04-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ22" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AR22" t="n">
         <x:v>0</x:v>
@@ -4087,13 +4113,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AU22" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AV22" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AW22" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AX22" t="n">
         <x:v>630</x:v>
@@ -4108,13 +4134,13 @@
         <x:v>Joint US-Israel</x:v>
       </x:c>
       <x:c r="B23" s="18" t="str">
-        <x:v>Iran’s top university bombed as US, Israel intensify attacks</x:v>
+        <x:v>US-Israeli strikes kill Iran Guards intelligence chief: Guards</x:v>
       </x:c>
       <x:c r="C23" t="n">
-        <x:v>629306</x:v>
+        <x:v>629305</x:v>
       </x:c>
       <x:c r="D23" t="str">
-        <x:v>IRN-2026-1-18868-88</x:v>
+        <x:v>IRN-2026-1-18868-87</x:v>
       </x:c>
       <x:c r="E23" t="n">
         <x:v>2026</x:v>
@@ -4166,43 +4192,43 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V23" t="str">
-        <x:v>"Al Jazeera English,2026-04-06,Iran’s top university bombed as US, Israel intensify attacks; 34 killed"</x:v>
+        <x:v>"Agence France Presse,2026-04-06,US-Israeli strikes kill Iran Guards intelligence chief: Guards"</x:v>
       </x:c>
       <x:c r="W23" t="str">
-        <x:v>Al Jazeera English</x:v>
+        <x:v>Agence France Presse</x:v>
       </x:c>
       <x:c r="X23" t="str">
         <x:v>2026-04-06</x:v>
       </x:c>
       <x:c r="Y23" t="str">
-        <x:v>Iran’s top university bombed as US, Israel intensify attacks; 34 killed</x:v>
+        <x:v>US-Israeli strikes kill Iran Guards intelligence chief: Guards</x:v>
       </x:c>
       <x:c r="Z23" t="str">
-        <x:v>Fars news agency</x:v>
+        <x:v>IRGC</x:v>
       </x:c>
       <x:c r="AA23" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB23" t="str">
-        <x:v>Baharestan county</x:v>
+        <x:v>Tehran city</x:v>
       </x:c>
       <x:c r="AC23" t="str">
-        <x:v>Baharestan County</x:v>
+        <x:v>Tehran</x:v>
       </x:c>
       <x:c r="AD23" t="str">
         <x:v>Tehran province</x:v>
       </x:c>
       <x:c r="AE23" t="str">
-        <x:v>Baharestan county</x:v>
+        <x:v>Tehran county</x:v>
       </x:c>
       <x:c r="AF23" t="n">
-        <x:v>35.53333</x:v>
+        <x:v>35.696111</x:v>
       </x:c>
       <x:c r="AG23" t="n">
-        <x:v>51.15</x:v>
+        <x:v>51.423056</x:v>
       </x:c>
       <x:c r="AH23" t="str">
-        <x:v>POINT (51.15 35.53333)</x:v>
+        <x:v>POINT (51.423056 35.696111)</x:v>
       </x:c>
       <x:c r="AI23" t="n">
         <x:v>181183</x:v>
@@ -4222,32 +4248,32 @@
       <x:c r="AN23" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO23" s="34" t="d">
+      <x:c r="AO23" s="36" t="d">
         <x:v>2026-04-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP23" s="30" t="d">
         <x:v>2026-04-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ23" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR23" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS23" t="n">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AT23" t="n">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AU23" t="n">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV23" t="n">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AW23" t="n">
-        <x:v>23</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX23" t="n">
         <x:v>630</x:v>
@@ -4265,10 +4291,10 @@
         <x:v>Iran’s top university bombed as US, Israel intensify attacks</x:v>
       </x:c>
       <x:c r="C24" t="n">
-        <x:v>629307</x:v>
+        <x:v>629306</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>IRN-2026-1-18868-91</x:v>
+        <x:v>IRN-2026-1-18868-88</x:v>
       </x:c>
       <x:c r="E24" t="n">
         <x:v>2026</x:v>
@@ -4332,34 +4358,34 @@
         <x:v>Iran’s top university bombed as US, Israel intensify attacks; 34 killed</x:v>
       </x:c>
       <x:c r="Z24" t="str">
-        <x:v>authorities</x:v>
+        <x:v>Fars news agency</x:v>
       </x:c>
       <x:c r="AA24" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AB24" t="str">
-        <x:v>Bandar Lengeh town</x:v>
+        <x:v>Baharestan county</x:v>
       </x:c>
       <x:c r="AC24" t="str">
-        <x:v>Bandar-e Lengeh</x:v>
+        <x:v>Baharestan County</x:v>
       </x:c>
       <x:c r="AD24" t="str">
-        <x:v>Hormozgan province</x:v>
+        <x:v>Tehran province</x:v>
       </x:c>
       <x:c r="AE24" t="str">
-        <x:v>Bandar Lengeh county</x:v>
+        <x:v>Baharestan county</x:v>
       </x:c>
       <x:c r="AF24" t="n">
-        <x:v>26.56777</x:v>
+        <x:v>35.53333</x:v>
       </x:c>
       <x:c r="AG24" t="n">
-        <x:v>54.893317</x:v>
+        <x:v>51.15</x:v>
       </x:c>
       <x:c r="AH24" t="str">
-        <x:v>POINT (54.893317 26.56777)</x:v>
+        <x:v>POINT (51.15 35.53333)</x:v>
       </x:c>
       <x:c r="AI24" t="n">
-        <x:v>168230</x:v>
+        <x:v>181183</x:v>
       </x:c>
       <x:c r="AJ24" t="str">
         <x:v>Iran</x:v>
@@ -4376,7 +4402,7 @@
       <x:c r="AN24" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO24" s="34" t="d">
+      <x:c r="AO24" s="36" t="d">
         <x:v>2026-04-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP24" s="30" t="d">
@@ -4389,19 +4415,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS24" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AT24" t="n">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AU24" t="n">
-        <x:v>6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AV24" t="n">
-        <x:v>6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AW24" t="n">
-        <x:v>6</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="AX24" t="n">
         <x:v>630</x:v>
@@ -4419,10 +4445,10 @@
         <x:v>Iran’s top university bombed as US, Israel intensify attacks</x:v>
       </x:c>
       <x:c r="C25" t="n">
-        <x:v>629308</x:v>
+        <x:v>629307</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>IRN-2026-1-18868-90</x:v>
+        <x:v>IRN-2026-1-18868-91</x:v>
       </x:c>
       <x:c r="E25" t="n">
         <x:v>2026</x:v>
@@ -4486,34 +4512,34 @@
         <x:v>Iran’s top university bombed as US, Israel intensify attacks; 34 killed</x:v>
       </x:c>
       <x:c r="Z25" t="str">
-        <x:v>political and security deputy of the governor, Morteza Heydari</x:v>
+        <x:v>authorities</x:v>
       </x:c>
       <x:c r="AA25" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AB25" t="str">
-        <x:v>Qom town</x:v>
+        <x:v>Bandar Lengeh town</x:v>
       </x:c>
       <x:c r="AC25" t="str">
-        <x:v>city of Qom</x:v>
+        <x:v>Bandar-e Lengeh</x:v>
       </x:c>
       <x:c r="AD25" t="str">
-        <x:v>Qom province</x:v>
+        <x:v>Hormozgan province</x:v>
       </x:c>
       <x:c r="AE25" t="str">
-        <x:v>Qom county</x:v>
+        <x:v>Bandar Lengeh county</x:v>
       </x:c>
       <x:c r="AF25" t="n">
-        <x:v>34.6401</x:v>
+        <x:v>26.56777</x:v>
       </x:c>
       <x:c r="AG25" t="n">
-        <x:v>50.8764</x:v>
+        <x:v>54.893317</x:v>
       </x:c>
       <x:c r="AH25" t="str">
-        <x:v>POINT (50.8764 34.6401)</x:v>
+        <x:v>POINT (54.893317 26.56777)</x:v>
       </x:c>
       <x:c r="AI25" t="n">
-        <x:v>179742</x:v>
+        <x:v>168230</x:v>
       </x:c>
       <x:c r="AJ25" t="str">
         <x:v>Iran</x:v>
@@ -4530,7 +4556,7 @@
       <x:c r="AN25" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO25" s="34" t="d">
+      <x:c r="AO25" s="36" t="d">
         <x:v>2026-04-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP25" s="30" t="d">
@@ -4546,16 +4572,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT25" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AU25" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AV25" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AW25" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AX25" t="n">
         <x:v>630</x:v>
@@ -4570,13 +4596,13 @@
         <x:v>Joint US-Israel</x:v>
       </x:c>
       <x:c r="B26" s="18" t="str">
-        <x:v>1st LD: 2 killed, 3 wounded in U.S.-Israeli attack on railway bridge in C. Iran</x:v>
+        <x:v>Iran’s top university bombed as US, Israel intensify attacks</x:v>
       </x:c>
       <x:c r="C26" t="n">
-        <x:v>629311</x:v>
+        <x:v>629308</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>IRN-2026-1-18868-94</x:v>
+        <x:v>IRN-2026-1-18868-90</x:v>
       </x:c>
       <x:c r="E26" t="n">
         <x:v>2026</x:v>
@@ -4585,7 +4611,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G26" t="str">
-        <x:v>Check geography</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="H26" t="n">
         <x:v>1</x:v>
@@ -4625,49 +4651,49 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U26" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V26" t="str">
-        <x:v>"Agence France Presse,2026-04-07,Two dead in attack on rail bridge in central Iran: regional official";"Xinhua News Agency,2026-04-07,1st LD: 2 killed, 3 wounded in U.S.-Israeli attack on railway bridge in C. Iran"</x:v>
+        <x:v>"Al Jazeera English,2026-04-06,Iran’s top university bombed as US, Israel intensify attacks; 34 killed"</x:v>
       </x:c>
       <x:c r="W26" t="str">
-        <x:v>Agence France Presse;Xinhua News Agency</x:v>
+        <x:v>Al Jazeera English</x:v>
       </x:c>
       <x:c r="X26" t="str">
-        <x:v>2026-04-07;2026-04-07</x:v>
+        <x:v>2026-04-06</x:v>
       </x:c>
       <x:c r="Y26" t="str">
-        <x:v>Two dead in attack on rail bridge in central Iran: regional official;1st LD: 2 killed, 3 wounded in U.S.-Israeli attack on railway bridge in C. Iran</x:v>
+        <x:v>Iran’s top university bombed as US, Israel intensify attacks; 34 killed</x:v>
       </x:c>
       <x:c r="Z26" t="str">
-        <x:v>senior regional security official in Isfahan province</x:v>
+        <x:v>political and security deputy of the governor, Morteza Heydari</x:v>
       </x:c>
       <x:c r="AA26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AB26" t="str">
-        <x:v>Kashan town</x:v>
+        <x:v>Qom town</x:v>
       </x:c>
       <x:c r="AC26" t="str">
-        <x:v>city of Kashan</x:v>
+        <x:v>city of Qom</x:v>
       </x:c>
       <x:c r="AD26" t="str">
-        <x:v>Esfahan province</x:v>
+        <x:v>Qom province</x:v>
       </x:c>
       <x:c r="AE26" t="str">
-        <x:v>Kashan county</x:v>
+        <x:v>Qom county</x:v>
       </x:c>
       <x:c r="AF26" t="n">
-        <x:v>33.98237</x:v>
+        <x:v>34.6401</x:v>
       </x:c>
       <x:c r="AG26" t="n">
-        <x:v>51.42769</x:v>
+        <x:v>50.8764</x:v>
       </x:c>
       <x:c r="AH26" t="str">
-        <x:v>POINT (51.42769 33.98237)</x:v>
+        <x:v>POINT (50.8764 34.6401)</x:v>
       </x:c>
       <x:c r="AI26" t="n">
-        <x:v>178303</x:v>
+        <x:v>179742</x:v>
       </x:c>
       <x:c r="AJ26" t="str">
         <x:v>Iran</x:v>
@@ -4684,11 +4710,11 @@
       <x:c r="AN26" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO26" s="34" t="d">
-        <x:v>2026-04-07T00:00:00.000Z</x:v>
+      <x:c r="AO26" s="36" t="d">
+        <x:v>2026-04-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP26" s="30" t="d">
-        <x:v>2026-04-07T00:00:00.000Z</x:v>
+        <x:v>2026-04-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ26" t="n">
         <x:v>0</x:v>
@@ -4700,16 +4726,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT26" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AU26" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AV26" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AW26" t="n">
-        <x:v>2</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AX26" t="n">
         <x:v>630</x:v>
@@ -4724,13 +4750,13 @@
         <x:v>Joint US-Israel</x:v>
       </x:c>
       <x:c r="B27" s="18" t="str">
-        <x:v>Synagogue in Tehran ‘completely destroyed’ in US-Israeli attack</x:v>
+        <x:v>1st LD: 2 killed, 3 wounded in U.S.-Israeli attack on railway bridge in C. Iran</x:v>
       </x:c>
       <x:c r="C27" t="n">
-        <x:v>629312</x:v>
+        <x:v>629311</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>IRN-2026-1-18868-97</x:v>
+        <x:v>IRN-2026-1-18868-94</x:v>
       </x:c>
       <x:c r="E27" t="n">
         <x:v>2026</x:v>
@@ -4739,7 +4765,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G27" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Check geography</x:v>
       </x:c>
       <x:c r="H27" t="n">
         <x:v>1</x:v>
@@ -4779,49 +4805,49 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U27" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V27" t="str">
-        <x:v>"Al Jazeera English,2026-04-07,Synagogue in Tehran ‘completely destroyed’ in US-Israeli attack"</x:v>
+        <x:v>"Agence France Presse,2026-04-07,Two dead in attack on rail bridge in central Iran: regional official";"Xinhua News Agency,2026-04-07,1st LD: 2 killed, 3 wounded in U.S.-Israeli attack on railway bridge in C. Iran"</x:v>
       </x:c>
       <x:c r="W27" t="str">
-        <x:v>Al Jazeera English</x:v>
+        <x:v>Agence France Presse;Xinhua News Agency</x:v>
       </x:c>
       <x:c r="X27" t="str">
-        <x:v>2026-04-07</x:v>
+        <x:v>2026-04-07;2026-04-07</x:v>
       </x:c>
       <x:c r="Y27" t="str">
-        <x:v>Synagogue in Tehran ‘completely destroyed’ in US-Israeli attack</x:v>
+        <x:v>Two dead in attack on rail bridge in central Iran: regional official;1st LD: 2 killed, 3 wounded in U.S.-Israeli attack on railway bridge in C. Iran</x:v>
       </x:c>
       <x:c r="Z27" t="str">
-        <x:v>local media</x:v>
+        <x:v>senior regional security official in Isfahan province</x:v>
       </x:c>
       <x:c r="AA27" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="AB27" t="str">
-        <x:v>Pardis town</x:v>
+        <x:v>Kashan town</x:v>
       </x:c>
       <x:c r="AC27" t="str">
-        <x:v>city of Pardis, east of Tehran</x:v>
+        <x:v>city of Kashan</x:v>
       </x:c>
       <x:c r="AD27" t="str">
-        <x:v>Tehran province</x:v>
+        <x:v>Esfahan province</x:v>
       </x:c>
       <x:c r="AE27" t="str">
-        <x:v>Pardis county</x:v>
+        <x:v>Kashan county</x:v>
       </x:c>
       <x:c r="AF27" t="n">
-        <x:v>35.74687</x:v>
+        <x:v>33.98237</x:v>
       </x:c>
       <x:c r="AG27" t="n">
-        <x:v>51.81222</x:v>
+        <x:v>51.42769</x:v>
       </x:c>
       <x:c r="AH27" t="str">
-        <x:v>POINT (51.81222 35.74687)</x:v>
+        <x:v>POINT (51.42769 33.98237)</x:v>
       </x:c>
       <x:c r="AI27" t="n">
-        <x:v>181184</x:v>
+        <x:v>178303</x:v>
       </x:c>
       <x:c r="AJ27" t="str">
         <x:v>Iran</x:v>
@@ -4836,34 +4862,34 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO27" s="36" t="d">
+        <x:v>2026-04-07T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="AP27" s="30" t="d">
+        <x:v>2026-04-07T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="AQ27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AT27" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AO27" s="34" t="d">
-        <x:v>2026-04-07T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="AP27" s="30" t="d">
-        <x:v>2026-04-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="AQ27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AR27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT27" t="n">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="AU27" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AV27" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AW27" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AX27" t="n">
         <x:v>630</x:v>
@@ -4881,10 +4907,10 @@
         <x:v>Synagogue in Tehran ‘completely destroyed’ in US-Israeli attack</x:v>
       </x:c>
       <x:c r="C28" t="n">
-        <x:v>629313</x:v>
+        <x:v>629312</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>IRN-2026-1-18868-96</x:v>
+        <x:v>IRN-2026-1-18868-97</x:v>
       </x:c>
       <x:c r="E28" t="n">
         <x:v>2026</x:v>
@@ -4954,28 +4980,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AB28" t="str">
-        <x:v>Shahriar town</x:v>
+        <x:v>Pardis town</x:v>
       </x:c>
       <x:c r="AC28" t="str">
-        <x:v>residential neighbourhood in the city of Shahriar</x:v>
+        <x:v>city of Pardis, east of Tehran</x:v>
       </x:c>
       <x:c r="AD28" t="str">
         <x:v>Tehran province</x:v>
       </x:c>
       <x:c r="AE28" t="str">
-        <x:v>Shahriar county</x:v>
+        <x:v>Pardis county</x:v>
       </x:c>
       <x:c r="AF28" t="n">
-        <x:v>35.65884</x:v>
+        <x:v>35.74687</x:v>
       </x:c>
       <x:c r="AG28" t="n">
-        <x:v>51.05775</x:v>
+        <x:v>51.81222</x:v>
       </x:c>
       <x:c r="AH28" t="str">
-        <x:v>POINT (51.05775 35.65884)</x:v>
+        <x:v>POINT (51.81222 35.74687)</x:v>
       </x:c>
       <x:c r="AI28" t="n">
-        <x:v>181183</x:v>
+        <x:v>181184</x:v>
       </x:c>
       <x:c r="AJ28" t="str">
         <x:v>Iran</x:v>
@@ -4992,7 +5018,7 @@
       <x:c r="AN28" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AO28" s="34" t="d">
+      <x:c r="AO28" s="36" t="d">
         <x:v>2026-04-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP28" s="30" t="d">
@@ -5008,16 +5034,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT28" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AU28" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AV28" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AW28" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AX28" t="n">
         <x:v>630</x:v>
@@ -5029,16 +5055,16 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="18" t="str">
-        <x:v>US</x:v>
+        <x:v>Joint US-Israel</x:v>
       </x:c>
       <x:c r="B29" s="18" t="str">
-        <x:v>Iran says US military killed five civilians in attacks on passenger boats</x:v>
+        <x:v>Synagogue in Tehran ‘completely destroyed’ in US-Israeli attack</x:v>
       </x:c>
       <x:c r="C29" t="n">
-        <x:v>629402</x:v>
+        <x:v>629313</x:v>
       </x:c>
       <x:c r="D29" t="str">
-        <x:v>IRN-2026-1-18868-102</x:v>
+        <x:v>IRN-2026-1-18868-96</x:v>
       </x:c>
       <x:c r="E29" t="n">
         <x:v>2026</x:v>
@@ -5047,7 +5073,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>Check geography</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="H29" t="n">
         <x:v>1</x:v>
@@ -5087,176 +5113,180 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V29" t="str">
+        <x:v>"Al Jazeera English,2026-04-07,Synagogue in Tehran ‘completely destroyed’ in US-Israeli attack"</x:v>
+      </x:c>
+      <x:c r="W29" t="str">
+        <x:v>Al Jazeera English</x:v>
+      </x:c>
+      <x:c r="X29" t="str">
+        <x:v>2026-04-07</x:v>
+      </x:c>
+      <x:c r="Y29" t="str">
+        <x:v>Synagogue in Tehran ‘completely destroyed’ in US-Israeli attack</x:v>
+      </x:c>
+      <x:c r="Z29" t="str">
+        <x:v>local media</x:v>
+      </x:c>
+      <x:c r="AA29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB29" t="str">
+        <x:v>Shahriar town</x:v>
+      </x:c>
+      <x:c r="AC29" t="str">
+        <x:v>residential neighbourhood in the city of Shahriar</x:v>
+      </x:c>
+      <x:c r="AD29" t="str">
+        <x:v>Tehran province</x:v>
+      </x:c>
+      <x:c r="AE29" t="str">
+        <x:v>Shahriar county</x:v>
+      </x:c>
+      <x:c r="AF29" t="n">
+        <x:v>35.65884</x:v>
+      </x:c>
+      <x:c r="AG29" t="n">
+        <x:v>51.05775</x:v>
+      </x:c>
+      <x:c r="AH29" t="str">
+        <x:v>POINT (51.05775 35.65884)</x:v>
+      </x:c>
+      <x:c r="AI29" t="n">
+        <x:v>181183</x:v>
+      </x:c>
+      <x:c r="AJ29" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="AK29" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="AL29" t="str">
+        <x:v>Middle East</x:v>
+      </x:c>
+      <x:c r="AM29" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN29" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="V29" t="str">
+      <x:c r="AO29" s="36" t="d">
+        <x:v>2026-04-07T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="AP29" s="30" t="d">
+        <x:v>2026-04-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="AQ29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AT29" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="AU29" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="AV29" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="AW29" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="AX29" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="AY29"/>
+      <x:c r="AZ29" t="str">
+        <x:v>26.01.26.06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="18" t="str">
+        <x:v>US</x:v>
+      </x:c>
+      <x:c r="B30" s="18" t="str">
+        <x:v>Iran says US military killed five civilians in attacks on passenger boats</x:v>
+      </x:c>
+      <x:c r="C30" t="n">
+        <x:v>629402</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>IRN-2026-1-18868-102</x:v>
+      </x:c>
+      <x:c r="E30" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>Check geography</x:v>
+      </x:c>
+      <x:c r="H30" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30"/>
+      <x:c r="J30" t="n">
+        <x:v>16905</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>Iran - Israel, United States of America</x:v>
+      </x:c>
+      <x:c r="L30" t="n">
+        <x:v>18868</x:v>
+      </x:c>
+      <x:c r="M30" t="n">
+        <x:v>18868</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
+        <x:v>Government of Iran - Government of Israel, Government of United States of America</x:v>
+      </x:c>
+      <x:c r="O30" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="P30" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="Q30" t="str">
+        <x:v>Government of Iran</x:v>
+      </x:c>
+      <x:c r="R30" t="n">
+        <x:v>9865</x:v>
+      </x:c>
+      <x:c r="S30" t="n">
+        <x:v>9865</x:v>
+      </x:c>
+      <x:c r="T30" t="str">
+        <x:v>Government of Israel, Government of United States of America</x:v>
+      </x:c>
+      <x:c r="U30" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="V30" t="str">
         <x:v>"Al Jazeera English,2026-05-05,Iran says US military killed five civilians in attacks on passenger boats";"BBC Monitoring News Alert,2026-05-05,Iran says US targeted civilian, not IRGC, boats, killing five people
 CR 
 Source: Fars News Agency, Tehran, in Persian 0603 GMT 5 May 26"</x:v>
       </x:c>
-      <x:c r="W29" t="str">
+      <x:c r="W30" t="str">
         <x:v>Al Jazeera English;BBC Monitoring News Alert</x:v>
       </x:c>
-      <x:c r="X29" t="str">
+      <x:c r="X30" t="str">
         <x:v>2026-05-05;2026-05-05</x:v>
       </x:c>
-      <x:c r="Y29" t="str">
+      <x:c r="Y30" t="str">
         <x:v>Iran says US military killed five civilians in attacks on passenger boats;Iran says US targeted civilian, not IRGC, boats, killing five people
 CR 
 Source: Fars News Agency, Tehran, in Persian 0603 GMT 5 May 26</x:v>
       </x:c>
-      <x:c r="Z29" t="str">
+      <x:c r="Z30" t="str">
         <x:v>IRGC commander, US Admiral Brad Cooper, unnamed military source</x:v>
-      </x:c>
-      <x:c r="AA29" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="AB29" t="str">
-        <x:v>Iran</x:v>
-      </x:c>
-      <x:c r="AC29" t="str">
-        <x:v>Strait of Hormuz, travelling from the Omani port of Khasab towards Iran's coast</x:v>
-      </x:c>
-      <x:c r="AD29"/>
-      <x:c r="AE29"/>
-      <x:c r="AF29" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="AG29" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="AH29" t="str">
-        <x:v>POINT (53 32)</x:v>
-      </x:c>
-      <x:c r="AI29" t="n">
-        <x:v>176147</x:v>
-      </x:c>
-      <x:c r="AJ29" t="str">
-        <x:v>Iran</x:v>
-      </x:c>
-      <x:c r="AK29" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="AL29" t="str">
-        <x:v>Middle East</x:v>
-      </x:c>
-      <x:c r="AM29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN29" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO29" s="34" t="d">
-        <x:v>2026-05-04T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="AP29" s="30" t="d">
-        <x:v>2026-05-04T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="AQ29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AR29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AT29" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AU29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AV29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AW29" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AX29" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="AY29"/>
-      <x:c r="AZ29" t="str">
-        <x:v>26.01.26.06</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="18" t="str">
-        <x:v>US</x:v>
-      </x:c>
-      <x:c r="B30" s="18" t="str">
-        <x:v>Iran says US attacks over three weeks killed 50, injured more than 500</x:v>
-      </x:c>
-      <x:c r="C30" t="n">
-        <x:v>637547</x:v>
-      </x:c>
-      <x:c r="D30" t="str">
-        <x:v>IRN-2026-1-18868-129</x:v>
-      </x:c>
-      <x:c r="E30" t="n">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="F30" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="G30" t="str">
-        <x:v>Check deaths</x:v>
-      </x:c>
-      <x:c r="H30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I30"/>
-      <x:c r="J30" t="n">
-        <x:v>16905</x:v>
-      </x:c>
-      <x:c r="K30" t="str">
-        <x:v>Iran - Israel, United States of America</x:v>
-      </x:c>
-      <x:c r="L30" t="n">
-        <x:v>18868</x:v>
-      </x:c>
-      <x:c r="M30" t="n">
-        <x:v>18868</x:v>
-      </x:c>
-      <x:c r="N30" t="str">
-        <x:v>Government of Iran - Government of Israel, Government of United States of America</x:v>
-      </x:c>
-      <x:c r="O30" t="n">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="P30" t="n">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="Q30" t="str">
-        <x:v>Government of Iran</x:v>
-      </x:c>
-      <x:c r="R30" t="n">
-        <x:v>9865</x:v>
-      </x:c>
-      <x:c r="S30" t="n">
-        <x:v>9865</x:v>
-      </x:c>
-      <x:c r="T30" t="str">
-        <x:v>Government of Israel, Government of United States of America</x:v>
-      </x:c>
-      <x:c r="U30" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="V30" t="str">
-        <x:v>"BBC Monitoring News Alert,2026-07-18,Iran says US attacks over three weeks killed 50, injured more than 500"</x:v>
-      </x:c>
-      <x:c r="W30" t="str">
-        <x:v>BBC Monitoring News Alert</x:v>
-      </x:c>
-      <x:c r="X30" t="str">
-        <x:v>2026-07-18</x:v>
-      </x:c>
-      <x:c r="Y30" t="str">
-        <x:v>Iran says US attacks over three weeks killed 50, injured more than 500</x:v>
-      </x:c>
-      <x:c r="Z30" t="str">
-        <x:v>Iran's Health Ministry</x:v>
       </x:c>
       <x:c r="AA30" t="n">
         <x:v>6</x:v>
@@ -5264,7 +5294,9 @@
       <x:c r="AB30" t="str">
         <x:v>Iran</x:v>
       </x:c>
-      <x:c r="AC30"/>
+      <x:c r="AC30" t="str">
+        <x:v>Strait of Hormuz, travelling from the Omani port of Khasab towards Iran's coast</x:v>
+      </x:c>
       <x:c r="AD30"/>
       <x:c r="AE30"/>
       <x:c r="AF30" t="n">
@@ -5289,16 +5321,16 @@
         <x:v>Middle East</x:v>
       </x:c>
       <x:c r="AM30" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AN30" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="AO30" s="34" t="d">
-        <x:v>2026-06-27T00:00:00.000Z</x:v>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO30" s="36" t="d">
+        <x:v>2026-05-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP30" s="30" t="d">
-        <x:v>2026-07-18T00:00:00.000Z</x:v>
+        <x:v>2026-05-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ30" t="n">
         <x:v>0</x:v>
@@ -5307,26 +5339,26 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS30" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AT30" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AU30" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AV30" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AW30" t="n">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="AX30" t="n">
         <x:v>630</x:v>
       </x:c>
       <x:c r="AY30"/>
       <x:c r="AZ30" t="str">
-        <x:v>26.0.7</x:v>
+        <x:v>26.01.26.06</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -5334,13 +5366,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B31" s="18" t="str">
-        <x:v>Iran state media says member of Revolutionary Guards killed in US strikes</x:v>
+        <x:v>Iran says US attacks over three weeks killed 50, injured more than 500</x:v>
       </x:c>
       <x:c r="C31" t="n">
-        <x:v>637517</x:v>
+        <x:v>637547</x:v>
       </x:c>
       <x:c r="D31" t="str">
-        <x:v>IRN-2026-1-18868-114</x:v>
+        <x:v>IRN-2026-1-18868-129</x:v>
       </x:c>
       <x:c r="E31" t="n">
         <x:v>2026</x:v>
@@ -5349,7 +5381,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G31" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Check deaths</x:v>
       </x:c>
       <x:c r="H31" t="n">
         <x:v>1</x:v>
@@ -5392,46 +5424,40 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V31" t="str">
-        <x:v>"Agence France Presse,2026-07-08,Iran state media says member of Revolutionary Guards killed in US strikes"</x:v>
+        <x:v>"BBC Monitoring News Alert,2026-07-18,Iran says US attacks over three weeks killed 50, injured more than 500"</x:v>
       </x:c>
       <x:c r="W31" t="str">
-        <x:v>Agence France Presse</x:v>
+        <x:v>BBC Monitoring News Alert</x:v>
       </x:c>
       <x:c r="X31" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-18</x:v>
       </x:c>
       <x:c r="Y31" t="str">
-        <x:v>Iran state media says member of Revolutionary Guards killed in US strikes</x:v>
+        <x:v>Iran says US attacks over three weeks killed 50, injured more than 500</x:v>
       </x:c>
       <x:c r="Z31" t="str">
-        <x:v>IRGC, IRNA news agency</x:v>
+        <x:v>Iran's Health Ministry</x:v>
       </x:c>
       <x:c r="AA31" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AB31" t="str">
-        <x:v>Bandar-e Mahshahr town</x:v>
-      </x:c>
-      <x:c r="AC31" t="str">
-        <x:v>Mahshahr, a port city</x:v>
-      </x:c>
-      <x:c r="AD31" t="str">
-        <x:v>Khuzestan province</x:v>
-      </x:c>
-      <x:c r="AE31" t="str">
-        <x:v>Bandar-e Mahshahr county</x:v>
-      </x:c>
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="AC31"/>
+      <x:c r="AD31"/>
+      <x:c r="AE31"/>
       <x:c r="AF31" t="n">
-        <x:v>30.5543</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AG31" t="n">
-        <x:v>49.18589</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH31" t="str">
-        <x:v>POINT (49.18589 30.5543)</x:v>
+        <x:v>POINT (53 32)</x:v>
       </x:c>
       <x:c r="AI31" t="n">
-        <x:v>173979</x:v>
+        <x:v>176147</x:v>
       </x:c>
       <x:c r="AJ31" t="str">
         <x:v>Iran</x:v>
@@ -5443,37 +5469,37 @@
         <x:v>Middle East</x:v>
       </x:c>
       <x:c r="AM31" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AN31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO31" s="34" t="d">
-        <x:v>2026-07-08T00:00:00.000Z</x:v>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AO31" s="36" t="d">
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP31" s="30" t="d">
-        <x:v>2026-07-08T00:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ31" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR31" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS31" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AT31" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AU31" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AV31" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AW31" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AX31" t="n">
         <x:v>630</x:v>
@@ -5488,13 +5514,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B32" s="18" t="str">
-        <x:v>Eight Iran military personnel killed in US strikes: state media</x:v>
+        <x:v>Iran state media says member of Revolutionary Guards killed in US strikes</x:v>
       </x:c>
       <x:c r="C32" t="n">
-        <x:v>637518</x:v>
+        <x:v>637517</x:v>
       </x:c>
       <x:c r="D32" t="str">
-        <x:v>IRN-2026-1-18868-115</x:v>
+        <x:v>IRN-2026-1-18868-114</x:v>
       </x:c>
       <x:c r="E32" t="n">
         <x:v>2026</x:v>
@@ -5546,7 +5572,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V32" t="str">
-        <x:v>"Agence France Presse,2026-07-08,Eight Iran military personnel killed in US strikes: state media"</x:v>
+        <x:v>"Agence France Presse,2026-07-08,Iran state media says member of Revolutionary Guards killed in US strikes"</x:v>
       </x:c>
       <x:c r="W32" t="str">
         <x:v>Agence France Presse</x:v>
@@ -5555,37 +5581,37 @@
         <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="Y32" t="str">
-        <x:v>Eight Iran military personnel killed in US strikes: state media</x:v>
+        <x:v>Iran state media says member of Revolutionary Guards killed in US strikes</x:v>
       </x:c>
       <x:c r="Z32" t="str">
-        <x:v>military, Iranian state TV</x:v>
+        <x:v>IRGC, IRNA news agency</x:v>
       </x:c>
       <x:c r="AA32" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB32" t="str">
-        <x:v>Bandar Abbas county</x:v>
+        <x:v>Bandar-e Mahshahr town</x:v>
       </x:c>
       <x:c r="AC32" t="str">
-        <x:v>Bandar Abbas</x:v>
+        <x:v>Mahshahr, a port city</x:v>
       </x:c>
       <x:c r="AD32" t="str">
-        <x:v>Hormozgan province</x:v>
+        <x:v>Khuzestan province</x:v>
       </x:c>
       <x:c r="AE32" t="str">
-        <x:v>Bandar Abbas county</x:v>
+        <x:v>Bandar-e Mahshahr county</x:v>
       </x:c>
       <x:c r="AF32" t="n">
-        <x:v>27.55</x:v>
+        <x:v>30.5543</x:v>
       </x:c>
       <x:c r="AG32" t="n">
-        <x:v>56.28333</x:v>
+        <x:v>49.18589</x:v>
       </x:c>
       <x:c r="AH32" t="str">
-        <x:v>POINT (56.28333 27.55)</x:v>
+        <x:v>POINT (49.18589 30.5543)</x:v>
       </x:c>
       <x:c r="AI32" t="n">
-        <x:v>169673</x:v>
+        <x:v>173979</x:v>
       </x:c>
       <x:c r="AJ32" t="str">
         <x:v>Iran</x:v>
@@ -5602,14 +5628,14 @@
       <x:c r="AN32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO32" s="34" t="d">
+      <x:c r="AO32" s="36" t="d">
         <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP32" s="30" t="d">
         <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ32" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR32" t="n">
         <x:v>0</x:v>
@@ -5621,13 +5647,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AU32" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV32" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AW32" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX32" t="n">
         <x:v>630</x:v>
@@ -5642,13 +5668,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B33" s="18" t="str">
-        <x:v>Iran army says eight members killed in latest US attack</x:v>
+        <x:v>Eight Iran military personnel killed in US strikes: state media</x:v>
       </x:c>
       <x:c r="C33" t="n">
-        <x:v>637519</x:v>
+        <x:v>637518</x:v>
       </x:c>
       <x:c r="D33" t="str">
-        <x:v>IRN-2026-1-18868-116</x:v>
+        <x:v>IRN-2026-1-18868-115</x:v>
       </x:c>
       <x:c r="E33" t="n">
         <x:v>2026</x:v>
@@ -5700,44 +5726,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V33" t="str">
-        <x:v>"BBC Monitoring News Alert,2026-07-08,Iran army says eight members killed in latest US attack"</x:v>
+        <x:v>"Agence France Presse,2026-07-08,Eight Iran military personnel killed in US strikes: state media"</x:v>
       </x:c>
       <x:c r="W33" t="str">
-        <x:v>BBC Monitoring News Alert</x:v>
+        <x:v>Agence France Presse</x:v>
       </x:c>
       <x:c r="X33" t="str">
         <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="Y33" t="str">
-        <x:v>Iran army says eight members killed in latest US attack</x:v>
+        <x:v>Eight Iran military personnel killed in US strikes: state media</x:v>
       </x:c>
       <x:c r="Z33" t="str">
-        <x:v>Iran's army</x:v>
+        <x:v>military, Iranian state TV</x:v>
       </x:c>
       <x:c r="AA33" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AB33" t="str">
-        <x:v>Bushehr province</x:v>
+        <x:v>Bandar Abbas county</x:v>
       </x:c>
       <x:c r="AC33" t="str">
-        <x:v>Bushehr</x:v>
+        <x:v>Bandar Abbas</x:v>
       </x:c>
       <x:c r="AD33" t="str">
-        <x:v>Bushehr province</x:v>
-      </x:c>
-      <x:c r="AE33"/>
+        <x:v>Hormozgan province</x:v>
+      </x:c>
+      <x:c r="AE33" t="str">
+        <x:v>Bandar Abbas county</x:v>
+      </x:c>
       <x:c r="AF33" t="n">
-        <x:v>28.9184</x:v>
+        <x:v>27.55</x:v>
       </x:c>
       <x:c r="AG33" t="n">
-        <x:v>50.8382</x:v>
+        <x:v>56.28333</x:v>
       </x:c>
       <x:c r="AH33" t="str">
-        <x:v>POINT (50.8382 28.9184)</x:v>
+        <x:v>POINT (56.28333 27.55)</x:v>
       </x:c>
       <x:c r="AI33" t="n">
-        <x:v>171102</x:v>
+        <x:v>169673</x:v>
       </x:c>
       <x:c r="AJ33" t="str">
         <x:v>Iran</x:v>
@@ -5754,14 +5782,14 @@
       <x:c r="AN33" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO33" s="34" t="d">
+      <x:c r="AO33" s="36" t="d">
         <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP33" s="30" t="d">
         <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ33" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AR33" t="n">
         <x:v>0</x:v>
@@ -5773,13 +5801,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AU33" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AV33" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AW33" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AX33" t="n">
         <x:v>630</x:v>
@@ -5794,13 +5822,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B34" s="18" t="str">
-        <x:v>Iran health ministry says 14 killed in two days of US strikes</x:v>
+        <x:v>Iran army says eight members killed in latest US attack</x:v>
       </x:c>
       <x:c r="C34" t="n">
-        <x:v>637521</x:v>
+        <x:v>637519</x:v>
       </x:c>
       <x:c r="D34" t="str">
-        <x:v>IRN-2026-1-18868-118</x:v>
+        <x:v>IRN-2026-1-18868-116</x:v>
       </x:c>
       <x:c r="E34" t="n">
         <x:v>2026</x:v>
@@ -5809,7 +5837,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G34" t="str">
-        <x:v>Check geography</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="H34" t="n">
         <x:v>1</x:v>
@@ -5852,40 +5880,44 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V34" t="str">
-        <x:v>"Agence France Presse,2026-07-09,Iran health ministry says 14 killed in two days of US strikes"</x:v>
+        <x:v>"BBC Monitoring News Alert,2026-07-08,Iran army says eight members killed in latest US attack"</x:v>
       </x:c>
       <x:c r="W34" t="str">
-        <x:v>Agence France Presse</x:v>
+        <x:v>BBC Monitoring News Alert</x:v>
       </x:c>
       <x:c r="X34" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="Y34" t="str">
-        <x:v>Iran health ministry says 14 killed in two days of US strikes</x:v>
+        <x:v>Iran army says eight members killed in latest US attack</x:v>
       </x:c>
       <x:c r="Z34" t="str">
-        <x:v>health ministry</x:v>
+        <x:v>Iran's army</x:v>
       </x:c>
       <x:c r="AA34" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB34" t="str">
-        <x:v>Iran</x:v>
-      </x:c>
-      <x:c r="AC34"/>
-      <x:c r="AD34"/>
+        <x:v>Bushehr province</x:v>
+      </x:c>
+      <x:c r="AC34" t="str">
+        <x:v>Bushehr</x:v>
+      </x:c>
+      <x:c r="AD34" t="str">
+        <x:v>Bushehr province</x:v>
+      </x:c>
       <x:c r="AE34"/>
       <x:c r="AF34" t="n">
-        <x:v>32</x:v>
+        <x:v>28.9184</x:v>
       </x:c>
       <x:c r="AG34" t="n">
-        <x:v>53</x:v>
+        <x:v>50.8382</x:v>
       </x:c>
       <x:c r="AH34" t="str">
-        <x:v>POINT (53 32)</x:v>
+        <x:v>POINT (50.8382 28.9184)</x:v>
       </x:c>
       <x:c r="AI34" t="n">
-        <x:v>176147</x:v>
+        <x:v>171102</x:v>
       </x:c>
       <x:c r="AJ34" t="str">
         <x:v>Iran</x:v>
@@ -5900,16 +5932,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN34" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="AO34" s="34" t="d">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO34" s="36" t="d">
         <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP34" s="30" t="d">
-        <x:v>2026-07-09T00:00:00.000Z</x:v>
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ34" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR34" t="n">
         <x:v>0</x:v>
@@ -5918,16 +5950,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT34" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AU34" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV34" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AW34" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX34" t="n">
         <x:v>630</x:v>
@@ -5942,13 +5974,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B35" s="18" t="str">
-        <x:v>US strikes Iran, vows to reimpose naval blockade</x:v>
+        <x:v>Iran health ministry says 14 killed in two days of US strikes</x:v>
       </x:c>
       <x:c r="C35" t="n">
-        <x:v>637534</x:v>
+        <x:v>637521</x:v>
       </x:c>
       <x:c r="D35" t="str">
-        <x:v>IRN-2026-1-18868-125</x:v>
+        <x:v>IRN-2026-1-18868-118</x:v>
       </x:c>
       <x:c r="E35" t="n">
         <x:v>2026</x:v>
@@ -5957,7 +5989,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Check geography</x:v>
       </x:c>
       <x:c r="H35" t="n">
         <x:v>1</x:v>
@@ -5997,25 +6029,22 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U35" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V35" t="str">
-        <x:v>"Agence France Presse,2026-07-14,US strikes Iran, vows to reimpose naval blockade";"Associated Press Newswires,2026-07-15,More than 30 people killed in U.S. airstrikes targeting Iran in "recent days," Iranian
-government spokesperson says"</x:v>
+        <x:v>"Agence France Presse,2026-07-09,Iran health ministry says 14 killed in two days of US strikes"</x:v>
       </x:c>
       <x:c r="W35" t="str">
-        <x:v>Agence France Presse;Associated Press Newswires</x:v>
+        <x:v>Agence France Presse</x:v>
       </x:c>
       <x:c r="X35" t="str">
-        <x:v>2026-07-14;2026-07-15</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="Y35" t="str">
-        <x:v>US strikes Iran, vows to reimpose naval blockade;More than 30 people killed in U.S. airstrikes targeting Iran in "recent days," Iranian
-government spokesperson says</x:v>
+        <x:v>Iran health ministry says 14 killed in two days of US strikes</x:v>
       </x:c>
       <x:c r="Z35" t="str">
-        <x:v>Iranian media and official announcements, AFP, Iranian
-government spokesperson</x:v>
+        <x:v>health ministry</x:v>
       </x:c>
       <x:c r="AA35" t="n">
         <x:v>6</x:v>
@@ -6051,13 +6080,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN35" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="AO35" s="34" t="d">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AO35" s="36" t="d">
         <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP35" s="30" t="d">
-        <x:v>2026-07-14T00:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ35" t="n">
         <x:v>0</x:v>
@@ -6069,16 +6098,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT35" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AU35" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AV35" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AW35" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AX35" t="n">
         <x:v>630</x:v>
@@ -6093,13 +6122,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B36" s="18" t="str">
-        <x:v>US strikes kill three in western Iran: Iranian state media</x:v>
+        <x:v>US strikes Iran, vows to reimpose naval blockade</x:v>
       </x:c>
       <x:c r="C36" t="n">
-        <x:v>637520</x:v>
+        <x:v>637534</x:v>
       </x:c>
       <x:c r="D36" t="str">
-        <x:v>IRN-2026-1-18868-117</x:v>
+        <x:v>IRN-2026-1-18868-125</x:v>
       </x:c>
       <x:c r="E36" t="n">
         <x:v>2026</x:v>
@@ -6148,49 +6177,46 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U36" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V36" t="str">
-        <x:v>"Agence France Presse,2026-07-09,US strikes kill three in western Iran: Iranian state media"</x:v>
+        <x:v>"Agence France Presse,2026-07-14,US strikes Iran, vows to reimpose naval blockade";"Associated Press Newswires,2026-07-15,More than 30 people killed in U.S. airstrikes targeting Iran in "recent days," Iranian
+government spokesperson says"</x:v>
       </x:c>
       <x:c r="W36" t="str">
-        <x:v>Agence France Presse</x:v>
+        <x:v>Agence France Presse;Associated Press Newswires</x:v>
       </x:c>
       <x:c r="X36" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-14;2026-07-15</x:v>
       </x:c>
       <x:c r="Y36" t="str">
-        <x:v>US strikes kill three in western Iran: Iranian state media</x:v>
+        <x:v>US strikes Iran, vows to reimpose naval blockade;More than 30 people killed in U.S. airstrikes targeting Iran in "recent days," Iranian
+government spokesperson says</x:v>
       </x:c>
       <x:c r="Z36" t="str">
-        <x:v>IRNA news agency, deputy governor of Khuzestan</x:v>
+        <x:v>Iranian media and official announcements, AFP, Iranian
+government spokesperson</x:v>
       </x:c>
       <x:c r="AA36" t="n">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AB36" t="str">
-        <x:v>Ahvaz town</x:v>
-      </x:c>
-      <x:c r="AC36" t="str">
-        <x:v>outskirts of city of Ahvaz</x:v>
-      </x:c>
-      <x:c r="AD36" t="str">
-        <x:v>Khuzestan province</x:v>
-      </x:c>
-      <x:c r="AE36" t="str">
-        <x:v>Ahvaz county</x:v>
-      </x:c>
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="AC36"/>
+      <x:c r="AD36"/>
+      <x:c r="AE36"/>
       <x:c r="AF36" t="n">
-        <x:v>31.320278</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AG36" t="n">
-        <x:v>48.669167</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AH36" t="str">
-        <x:v>POINT (48.669167 31.320278)</x:v>
+        <x:v>POINT (53 32)</x:v>
       </x:c>
       <x:c r="AI36" t="n">
-        <x:v>174698</x:v>
+        <x:v>176147</x:v>
       </x:c>
       <x:c r="AJ36" t="str">
         <x:v>Iran</x:v>
@@ -6205,16 +6231,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AN36" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO36" s="34" t="d">
-        <x:v>2026-07-09T00:00:00.000Z</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AO36" s="36" t="d">
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP36" s="30" t="d">
-        <x:v>2026-07-09T00:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ36" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR36" t="n">
         <x:v>0</x:v>
@@ -6223,16 +6249,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT36" t="n">
-        <x:v>0</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AU36" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AV36" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AW36" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AX36" t="n">
         <x:v>630</x:v>
@@ -6247,13 +6273,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B37" s="18" t="str">
-        <x:v>Overnight US strikes killed Iranian soldier: media</x:v>
+        <x:v>US strikes kill three in western Iran: Iranian state media</x:v>
       </x:c>
       <x:c r="C37" t="n">
-        <x:v>637523</x:v>
+        <x:v>637520</x:v>
       </x:c>
       <x:c r="D37" t="str">
-        <x:v>IRN-2026-1-18868-119</x:v>
+        <x:v>IRN-2026-1-18868-117</x:v>
       </x:c>
       <x:c r="E37" t="n">
         <x:v>2026</x:v>
@@ -6305,46 +6331,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V37" t="str">
-        <x:v>"Agence France Presse,2026-07-12,Overnight US strikes killed Iranian soldier: media"</x:v>
+        <x:v>"Agence France Presse,2026-07-09,US strikes kill three in western Iran: Iranian state media"</x:v>
       </x:c>
       <x:c r="W37" t="str">
         <x:v>Agence France Presse</x:v>
       </x:c>
       <x:c r="X37" t="str">
-        <x:v>2026-07-12</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="Y37" t="str">
-        <x:v>Overnight US strikes killed Iranian soldier: media</x:v>
+        <x:v>US strikes kill three in western Iran: Iranian state media</x:v>
       </x:c>
       <x:c r="Z37" t="str">
-        <x:v>local official, Mehr and Tasnim news agencies</x:v>
+        <x:v>IRNA news agency, deputy governor of Khuzestan</x:v>
       </x:c>
       <x:c r="AA37" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AB37" t="str">
-        <x:v>Bandar-e Jask town</x:v>
+        <x:v>Ahvaz town</x:v>
       </x:c>
       <x:c r="AC37" t="str">
-        <x:v>port of Jask</x:v>
+        <x:v>outskirts of city of Ahvaz</x:v>
       </x:c>
       <x:c r="AD37" t="str">
-        <x:v>Hormozgan province</x:v>
+        <x:v>Khuzestan province</x:v>
       </x:c>
       <x:c r="AE37" t="str">
-        <x:v>Jask county</x:v>
+        <x:v>Ahvaz county</x:v>
       </x:c>
       <x:c r="AF37" t="n">
-        <x:v>25.648133</x:v>
+        <x:v>31.320278</x:v>
       </x:c>
       <x:c r="AG37" t="n">
-        <x:v>57.779986</x:v>
+        <x:v>48.669167</x:v>
       </x:c>
       <x:c r="AH37" t="str">
-        <x:v>POINT (57.779986 25.648133)</x:v>
+        <x:v>POINT (48.669167 31.320278)</x:v>
       </x:c>
       <x:c r="AI37" t="n">
-        <x:v>166796</x:v>
+        <x:v>174698</x:v>
       </x:c>
       <x:c r="AJ37" t="str">
         <x:v>Iran</x:v>
@@ -6361,14 +6387,14 @@
       <x:c r="AN37" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO37" s="34" t="d">
-        <x:v>2026-07-12T00:00:00.000Z</x:v>
+      <x:c r="AO37" s="36" t="d">
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP37" s="30" t="d">
-        <x:v>2026-07-12T00:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ37" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AR37" t="n">
         <x:v>0</x:v>
@@ -6380,13 +6406,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AU37" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AV37" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AW37" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AX37" t="n">
         <x:v>630</x:v>
@@ -6401,13 +6427,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B38" s="18" t="str">
-        <x:v>US strikes kill one, wound 4 in southwest Iran: state media</x:v>
+        <x:v>Overnight US strikes killed Iranian soldier: media</x:v>
       </x:c>
       <x:c r="C38" t="n">
-        <x:v>637526</x:v>
+        <x:v>637523</x:v>
       </x:c>
       <x:c r="D38" t="str">
-        <x:v>IRN-2026-1-18868-122</x:v>
+        <x:v>IRN-2026-1-18868-119</x:v>
       </x:c>
       <x:c r="E38" t="n">
         <x:v>2026</x:v>
@@ -6456,49 +6482,49 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U38" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V38" t="str">
-        <x:v>"Agence France Presse,2026-07-13,US strikes kill one, wound 4 in southwest Iran: state media";"Agence France Presse,2026-07-13,US strikes kill two in southwest Iran: local media";"BBC Monitoring News Alert,2026-07-13,Three soldiers killed in US air strike in south-western Iran"</x:v>
+        <x:v>"Agence France Presse,2026-07-12,Overnight US strikes killed Iranian soldier: media"</x:v>
       </x:c>
       <x:c r="W38" t="str">
-        <x:v>Agence France Presse;Agence France Presse;BBC Monitoring News Alert</x:v>
+        <x:v>Agence France Presse</x:v>
       </x:c>
       <x:c r="X38" t="str">
-        <x:v>2026-07-13;2026-07-13;2026-07-13</x:v>
+        <x:v>2026-07-12</x:v>
       </x:c>
       <x:c r="Y38" t="str">
-        <x:v>US strikes kill one, wound 4 in southwest Iran: state media;US strikes kill two in southwest Iran: local media;Three soldiers killed in US air strike in south-western Iran</x:v>
+        <x:v>Overnight US strikes killed Iranian soldier: media</x:v>
       </x:c>
       <x:c r="Z38" t="str">
-        <x:v>Khuzestan province's deputy governor for security and law enforcement, media</x:v>
+        <x:v>local official, Mehr and Tasnim news agencies</x:v>
       </x:c>
       <x:c r="AA38" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB38" t="str">
-        <x:v>Abadan town</x:v>
+        <x:v>Bandar-e Jask town</x:v>
       </x:c>
       <x:c r="AC38" t="str">
-        <x:v>"three different locations" on the outskirts of the city of Abadan.</x:v>
+        <x:v>port of Jask</x:v>
       </x:c>
       <x:c r="AD38" t="str">
-        <x:v>Khuzestan province</x:v>
+        <x:v>Hormozgan province</x:v>
       </x:c>
       <x:c r="AE38" t="str">
-        <x:v>Abadan county</x:v>
+        <x:v>Jask county</x:v>
       </x:c>
       <x:c r="AF38" t="n">
-        <x:v>30.350556</x:v>
+        <x:v>25.648133</x:v>
       </x:c>
       <x:c r="AG38" t="n">
-        <x:v>48.283333</x:v>
+        <x:v>57.779986</x:v>
       </x:c>
       <x:c r="AH38" t="str">
-        <x:v>POINT (48.283333 30.350556)</x:v>
+        <x:v>POINT (57.779986 25.648133)</x:v>
       </x:c>
       <x:c r="AI38" t="n">
-        <x:v>173257</x:v>
+        <x:v>166796</x:v>
       </x:c>
       <x:c r="AJ38" t="str">
         <x:v>Iran</x:v>
@@ -6515,14 +6541,14 @@
       <x:c r="AN38" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO38" s="34" t="d">
-        <x:v>2026-07-13T00:00:00.000Z</x:v>
+      <x:c r="AO38" s="36" t="d">
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP38" s="30" t="d">
-        <x:v>2026-07-13T00:00:00.000Z</x:v>
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ38" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AR38" t="n">
         <x:v>0</x:v>
@@ -6534,13 +6560,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AU38" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV38" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AW38" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX38" t="n">
         <x:v>630</x:v>
@@ -6555,13 +6581,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B39" s="18" t="str">
-        <x:v>Several killed in latest U.S. strikes on Iran</x:v>
+        <x:v>US strikes kill one, wound 4 in southwest Iran: state media</x:v>
       </x:c>
       <x:c r="C39" t="n">
-        <x:v>637528</x:v>
+        <x:v>637526</x:v>
       </x:c>
       <x:c r="D39" t="str">
-        <x:v>IRN-2026-1-18868-123</x:v>
+        <x:v>IRN-2026-1-18868-122</x:v>
       </x:c>
       <x:c r="E39" t="n">
         <x:v>2026</x:v>
@@ -6610,50 +6636,49 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U39" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V39" t="str">
-        <x:v>"Xinhua News Agency,2026-07-13,Several killed in latest U.S. strikes on Iran"</x:v>
+        <x:v>"Agence France Presse,2026-07-13,US strikes kill one, wound 4 in southwest Iran: state media";"Agence France Presse,2026-07-13,US strikes kill two in southwest Iran: local media";"BBC Monitoring News Alert,2026-07-13,Three soldiers killed in US air strike in south-western Iran"</x:v>
       </x:c>
       <x:c r="W39" t="str">
-        <x:v>Xinhua News Agency</x:v>
+        <x:v>Agence France Presse;Agence France Presse;BBC Monitoring News Alert</x:v>
       </x:c>
       <x:c r="X39" t="str">
-        <x:v>2026-07-13</x:v>
+        <x:v>2026-07-13;2026-07-13;2026-07-13</x:v>
       </x:c>
       <x:c r="Y39" t="str">
-        <x:v>Several killed in latest U.S. strikes on Iran</x:v>
+        <x:v>US strikes kill one, wound 4 in southwest Iran: state media;US strikes kill two in southwest Iran: local media;Three soldiers killed in US air strike in south-western Iran</x:v>
       </x:c>
       <x:c r="Z39" t="str">
-        <x:v>Khuzestan's deputy
-governor for security and law enforcement affairs</x:v>
+        <x:v>Khuzestan province's deputy governor for security and law enforcement, media</x:v>
       </x:c>
       <x:c r="AA39" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AB39" t="str">
-        <x:v>Bandar-e Mahshahr town</x:v>
+        <x:v>Abadan town</x:v>
       </x:c>
       <x:c r="AC39" t="str">
-        <x:v>Bandar-e Mahshahr County in Khuzestan</x:v>
+        <x:v>"three different locations" on the outskirts of the city of Abadan.</x:v>
       </x:c>
       <x:c r="AD39" t="str">
         <x:v>Khuzestan province</x:v>
       </x:c>
       <x:c r="AE39" t="str">
-        <x:v>Bandar-e Mahshahr county</x:v>
+        <x:v>Abadan county</x:v>
       </x:c>
       <x:c r="AF39" t="n">
-        <x:v>30.5543</x:v>
+        <x:v>30.350556</x:v>
       </x:c>
       <x:c r="AG39" t="n">
-        <x:v>49.18589</x:v>
+        <x:v>48.283333</x:v>
       </x:c>
       <x:c r="AH39" t="str">
-        <x:v>POINT (49.18589 30.5543)</x:v>
+        <x:v>POINT (48.283333 30.350556)</x:v>
       </x:c>
       <x:c r="AI39" t="n">
-        <x:v>173979</x:v>
+        <x:v>173257</x:v>
       </x:c>
       <x:c r="AJ39" t="str">
         <x:v>Iran</x:v>
@@ -6670,14 +6695,14 @@
       <x:c r="AN39" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO39" s="34" t="d">
+      <x:c r="AO39" s="36" t="d">
         <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP39" s="30" t="d">
         <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ39" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AR39" t="n">
         <x:v>0</x:v>
@@ -6686,16 +6711,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT39" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AU39" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AV39" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AW39" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AX39" t="n">
         <x:v>630</x:v>
@@ -6710,13 +6735,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B40" s="18" t="str">
-        <x:v>3rd LD: At least 3 killed, 4 injured in fresh U.S. strikes on Iran -- media</x:v>
+        <x:v>Several killed in latest U.S. strikes on Iran</x:v>
       </x:c>
       <x:c r="C40" t="n">
-        <x:v>637532</x:v>
+        <x:v>637528</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>IRN-2026-1-18868-124</x:v>
+        <x:v>IRN-2026-1-18868-123</x:v>
       </x:c>
       <x:c r="E40" t="n">
         <x:v>2026</x:v>
@@ -6725,7 +6750,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>Check geography</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="H40" t="n">
         <x:v>1</x:v>
@@ -6768,44 +6793,47 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V40" t="str">
-        <x:v>"Xinhua News Agency,2026-07-14,3rd LD: At least 3 killed, 4 injured in fresh U.S. strikes on Iran -- media"</x:v>
+        <x:v>"Xinhua News Agency,2026-07-13,Several killed in latest U.S. strikes on Iran"</x:v>
       </x:c>
       <x:c r="W40" t="str">
         <x:v>Xinhua News Agency</x:v>
       </x:c>
       <x:c r="X40" t="str">
-        <x:v>2026-07-14</x:v>
+        <x:v>2026-07-13</x:v>
       </x:c>
       <x:c r="Y40" t="str">
-        <x:v>3rd LD: At least 3 killed, 4 injured in fresh U.S. strikes on Iran -- media</x:v>
+        <x:v>Several killed in latest U.S. strikes on Iran</x:v>
       </x:c>
       <x:c r="Z40" t="str">
-        <x:v>state-run IRIB news agency</x:v>
+        <x:v>Khuzestan's deputy
+governor for security and law enforcement affairs</x:v>
       </x:c>
       <x:c r="AA40" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB40" t="str">
-        <x:v>Hormozgan province</x:v>
+        <x:v>Bandar-e Mahshahr town</x:v>
       </x:c>
       <x:c r="AC40" t="str">
-        <x:v>a Hormozgan village</x:v>
+        <x:v>Bandar-e Mahshahr County in Khuzestan</x:v>
       </x:c>
       <x:c r="AD40" t="str">
-        <x:v>Hormozgan province</x:v>
-      </x:c>
-      <x:c r="AE40"/>
+        <x:v>Khuzestan province</x:v>
+      </x:c>
+      <x:c r="AE40" t="str">
+        <x:v>Bandar-e Mahshahr county</x:v>
+      </x:c>
       <x:c r="AF40" t="n">
-        <x:v>27.1884</x:v>
+        <x:v>30.5543</x:v>
       </x:c>
       <x:c r="AG40" t="n">
-        <x:v>56.2768</x:v>
+        <x:v>49.18589</x:v>
       </x:c>
       <x:c r="AH40" t="str">
-        <x:v>POINT (56.2768 27.1884)</x:v>
+        <x:v>POINT (49.18589 30.5543)</x:v>
       </x:c>
       <x:c r="AI40" t="n">
-        <x:v>168953</x:v>
+        <x:v>173979</x:v>
       </x:c>
       <x:c r="AJ40" t="str">
         <x:v>Iran</x:v>
@@ -6822,11 +6850,11 @@
       <x:c r="AN40" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO40" s="34" t="d">
-        <x:v>2026-07-14T00:00:00.000Z</x:v>
+      <x:c r="AO40" s="36" t="d">
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP40" s="30" t="d">
-        <x:v>2026-07-14T00:00:00.000Z</x:v>
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ40" t="n">
         <x:v>0</x:v>
@@ -6835,19 +6863,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS40" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AT40" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AU40" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV40" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AW40" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX40" t="n">
         <x:v>630</x:v>
@@ -6862,13 +6890,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B41" s="18" t="str">
-        <x:v>US strikes killed seven military personnel in southeast: Iran army</x:v>
+        <x:v>3rd LD: At least 3 killed, 4 injured in fresh U.S. strikes on Iran -- media</x:v>
       </x:c>
       <x:c r="C41" t="n">
-        <x:v>637540</x:v>
+        <x:v>637532</x:v>
       </x:c>
       <x:c r="D41" t="str">
-        <x:v>IRN-2026-1-18868-126</x:v>
+        <x:v>IRN-2026-1-18868-124</x:v>
       </x:c>
       <x:c r="E41" t="n">
         <x:v>2026</x:v>
@@ -6877,7 +6905,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>Clear</x:v>
+        <x:v>Check geography</x:v>
       </x:c>
       <x:c r="H41" t="n">
         <x:v>1</x:v>
@@ -6917,49 +6945,47 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U41" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V41" t="str">
-        <x:v>"Agence France Presse,2026-07-15,US strikes killed seven military personnel in southeast: Iran army";"Xinhua News Agency,2026-07-15,Iran says over 30 civilians killed in recent U.S. attacks"</x:v>
+        <x:v>"Xinhua News Agency,2026-07-14,3rd LD: At least 3 killed, 4 injured in fresh U.S. strikes on Iran -- media"</x:v>
       </x:c>
       <x:c r="W41" t="str">
-        <x:v>Agence France Presse;Xinhua News Agency</x:v>
+        <x:v>Xinhua News Agency</x:v>
       </x:c>
       <x:c r="X41" t="str">
-        <x:v>2026-07-15;2026-07-15</x:v>
+        <x:v>2026-07-14</x:v>
       </x:c>
       <x:c r="Y41" t="str">
-        <x:v>US strikes killed seven military personnel in southeast: Iran army;Iran says over 30 civilians killed in recent U.S. attacks</x:v>
+        <x:v>3rd LD: At least 3 killed, 4 injured in fresh U.S. strikes on Iran -- media</x:v>
       </x:c>
       <x:c r="Z41" t="str">
-        <x:v>Iranian army</x:v>
+        <x:v>state-run IRIB news agency</x:v>
       </x:c>
       <x:c r="AA41" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB41" t="str">
-        <x:v>Bampur county</x:v>
+        <x:v>Hormozgan province</x:v>
       </x:c>
       <x:c r="AC41" t="str">
-        <x:v>Bampur County</x:v>
+        <x:v>a Hormozgan village</x:v>
       </x:c>
       <x:c r="AD41" t="str">
-        <x:v>Sistan and Baluchestan province</x:v>
-      </x:c>
-      <x:c r="AE41" t="str">
-        <x:v>Bampur county</x:v>
-      </x:c>
+        <x:v>Hormozgan province</x:v>
+      </x:c>
+      <x:c r="AE41"/>
       <x:c r="AF41" t="n">
-        <x:v>27.168056</x:v>
+        <x:v>27.1884</x:v>
       </x:c>
       <x:c r="AG41" t="n">
-        <x:v>60.222778</x:v>
+        <x:v>56.2768</x:v>
       </x:c>
       <x:c r="AH41" t="str">
-        <x:v>POINT (60.222778 27.168056)</x:v>
+        <x:v>POINT (56.2768 27.1884)</x:v>
       </x:c>
       <x:c r="AI41" t="n">
-        <x:v>168961</x:v>
+        <x:v>168953</x:v>
       </x:c>
       <x:c r="AJ41" t="str">
         <x:v>Iran</x:v>
@@ -6976,32 +7002,32 @@
       <x:c r="AN41" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO41" s="34" t="d">
-        <x:v>2026-07-15T00:00:00.000Z</x:v>
+      <x:c r="AO41" s="36" t="d">
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP41" s="30" t="d">
-        <x:v>2026-07-15T00:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ41" t="n">
-        <x:v>7</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AR41" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS41" t="n">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AT41" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AU41" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AV41" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AW41" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AX41" t="n">
         <x:v>630</x:v>
@@ -7016,14 +7042,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B42" s="18" t="str">
-        <x:v>At least 7 people killed as US airstrikes target bridges in southern Iran, Iranian state
-television reports</x:v>
+        <x:v>US strikes killed seven military personnel in southeast: Iran army</x:v>
       </x:c>
       <x:c r="C42" t="n">
-        <x:v>637542</x:v>
+        <x:v>637540</x:v>
       </x:c>
       <x:c r="D42" t="str">
-        <x:v>IRN-2026-1-18868-127</x:v>
+        <x:v>IRN-2026-1-18868-126</x:v>
       </x:c>
       <x:c r="E42" t="n">
         <x:v>2026</x:v>
@@ -7075,48 +7100,46 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="V42" t="str">
-        <x:v>"Associated Press Newswires,2026-07-17,At least 7 people killed as US airstrikes target bridges in southern Iran, Iranian state
-television reports";"Xinhua News Agency,2026-07-16,2nd LD: 1 killed, 7 wounded in fresh U.S. strikes against S. Iran -- media"</x:v>
+        <x:v>"Agence France Presse,2026-07-15,US strikes killed seven military personnel in southeast: Iran army";"Xinhua News Agency,2026-07-15,Iran says over 30 civilians killed in recent U.S. attacks"</x:v>
       </x:c>
       <x:c r="W42" t="str">
-        <x:v>Associated Press Newswires;Xinhua News Agency</x:v>
+        <x:v>Agence France Presse;Xinhua News Agency</x:v>
       </x:c>
       <x:c r="X42" t="str">
-        <x:v>2026-07-17;2026-07-16</x:v>
+        <x:v>2026-07-15;2026-07-15</x:v>
       </x:c>
       <x:c r="Y42" t="str">
-        <x:v>At least 7 people killed as US airstrikes target bridges in southern Iran, Iranian state
-television reports;2nd LD: 1 killed, 7 wounded in fresh U.S. strikes against S. Iran -- media</x:v>
+        <x:v>US strikes killed seven military personnel in southeast: Iran army;Iran says over 30 civilians killed in recent U.S. attacks</x:v>
       </x:c>
       <x:c r="Z42" t="str">
-        <x:v>state-run IRIB news agency</x:v>
+        <x:v>Iranian army</x:v>
       </x:c>
       <x:c r="AA42" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="AB42" t="str">
-        <x:v>Khamir county</x:v>
+        <x:v>Bampur county</x:v>
       </x:c>
       <x:c r="AC42" t="str">
-        <x:v>Bandar Khamir County</x:v>
+        <x:v>Bampur County</x:v>
       </x:c>
       <x:c r="AD42" t="str">
-        <x:v>Hormozgan province</x:v>
+        <x:v>Sistan and Baluchestan province</x:v>
       </x:c>
       <x:c r="AE42" t="str">
-        <x:v>Khamir county</x:v>
+        <x:v>Bampur county</x:v>
       </x:c>
       <x:c r="AF42" t="n">
-        <x:v>27.27756</x:v>
+        <x:v>27.168056</x:v>
       </x:c>
       <x:c r="AG42" t="n">
-        <x:v>55.50915</x:v>
+        <x:v>60.222778</x:v>
       </x:c>
       <x:c r="AH42" t="str">
-        <x:v>POINT (55.50915 27.27756)</x:v>
+        <x:v>POINT (60.222778 27.168056)</x:v>
       </x:c>
       <x:c r="AI42" t="n">
-        <x:v>168952</x:v>
+        <x:v>168961</x:v>
       </x:c>
       <x:c r="AJ42" t="str">
         <x:v>Iran</x:v>
@@ -7133,23 +7156,23 @@
       <x:c r="AN42" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO42" s="34" t="d">
-        <x:v>2026-07-16T00:00:00.000Z</x:v>
+      <x:c r="AO42" s="36" t="d">
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP42" s="30" t="d">
-        <x:v>2026-07-16T00:00:00.000Z</x:v>
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ42" t="n">
-        <x:v>0</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AR42" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS42" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AT42" t="n">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AU42" t="n">
         <x:v>7</x:v>
@@ -7173,13 +7196,14 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B43" s="18" t="str">
-        <x:v>US strikes kill 3, wound 8 in southern Iran: Iranian state media</x:v>
+        <x:v>At least 7 people killed as US airstrikes target bridges in southern Iran, Iranian state
+television reports</x:v>
       </x:c>
       <x:c r="C43" t="n">
-        <x:v>637545</x:v>
+        <x:v>637542</x:v>
       </x:c>
       <x:c r="D43" t="str">
-        <x:v>IRN-2026-1-18868-128</x:v>
+        <x:v>IRN-2026-1-18868-127</x:v>
       </x:c>
       <x:c r="E43" t="n">
         <x:v>2026</x:v>
@@ -7228,47 +7252,51 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U43" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="V43" t="str">
-        <x:v>"Agence France Presse,2026-07-18,US strikes kill 3, wound 8 in southern Iran: Iranian state media"</x:v>
+        <x:v>"Associated Press Newswires,2026-07-17,At least 7 people killed as US airstrikes target bridges in southern Iran, Iranian state
+television reports";"Xinhua News Agency,2026-07-16,2nd LD: 1 killed, 7 wounded in fresh U.S. strikes against S. Iran -- media"</x:v>
       </x:c>
       <x:c r="W43" t="str">
-        <x:v>Agence France Presse</x:v>
+        <x:v>Associated Press Newswires;Xinhua News Agency</x:v>
       </x:c>
       <x:c r="X43" t="str">
-        <x:v>2026-07-18</x:v>
+        <x:v>2026-07-17;2026-07-16</x:v>
       </x:c>
       <x:c r="Y43" t="str">
-        <x:v>US strikes kill 3, wound 8 in southern Iran: Iranian state media</x:v>
+        <x:v>At least 7 people killed as US airstrikes target bridges in southern Iran, Iranian state
+television reports;2nd LD: 1 killed, 7 wounded in fresh U.S. strikes against S. Iran -- media</x:v>
       </x:c>
       <x:c r="Z43" t="str">
-        <x:v>deputy political, security and social affairs governor of Hormozgan</x:v>
+        <x:v>state-run IRIB news agency</x:v>
       </x:c>
       <x:c r="AA43" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AB43" t="str">
-        <x:v>Hormozgan province</x:v>
+        <x:v>Khamir county</x:v>
       </x:c>
       <x:c r="AC43" t="str">
-        <x:v>Hormozgan province</x:v>
+        <x:v>Bandar Khamir County</x:v>
       </x:c>
       <x:c r="AD43" t="str">
         <x:v>Hormozgan province</x:v>
       </x:c>
-      <x:c r="AE43"/>
+      <x:c r="AE43" t="str">
+        <x:v>Khamir county</x:v>
+      </x:c>
       <x:c r="AF43" t="n">
-        <x:v>27.1884</x:v>
+        <x:v>27.27756</x:v>
       </x:c>
       <x:c r="AG43" t="n">
-        <x:v>56.2768</x:v>
+        <x:v>55.50915</x:v>
       </x:c>
       <x:c r="AH43" t="str">
-        <x:v>POINT (56.2768 27.1884)</x:v>
+        <x:v>POINT (55.50915 27.27756)</x:v>
       </x:c>
       <x:c r="AI43" t="n">
-        <x:v>168953</x:v>
+        <x:v>168952</x:v>
       </x:c>
       <x:c r="AJ43" t="str">
         <x:v>Iran</x:v>
@@ -7285,11 +7313,11 @@
       <x:c r="AN43" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO43" s="34" t="d">
-        <x:v>2026-07-18T00:00:00.000Z</x:v>
+      <x:c r="AO43" s="36" t="d">
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP43" s="30" t="d">
-        <x:v>2026-07-18T00:00:00.000Z</x:v>
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ43" t="n">
         <x:v>0</x:v>
@@ -7298,19 +7326,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS43" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AT43" t="n">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AU43" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AV43" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AW43" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="AX43" t="n">
         <x:v>630</x:v>
@@ -7325,13 +7353,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B44" s="18" t="str">
-        <x:v>1 killed, several wounded in U.S. overnight strikes on 2 provinces in Iran</x:v>
+        <x:v>US strikes kill 3, wound 8 in southern Iran: Iranian state media</x:v>
       </x:c>
       <x:c r="C44" t="n">
-        <x:v>637525</x:v>
+        <x:v>637545</x:v>
       </x:c>
       <x:c r="D44" t="str">
-        <x:v>IRN-2026-1-18868-121</x:v>
+        <x:v>IRN-2026-1-18868-128</x:v>
       </x:c>
       <x:c r="E44" t="n">
         <x:v>2026</x:v>
@@ -7383,46 +7411,44 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V44" t="str">
-        <x:v>"Xinhua News Agency,2026-07-20,1 killed, several wounded in U.S. overnight strikes on 2 provinces in Iran"</x:v>
+        <x:v>"Agence France Presse,2026-07-18,US strikes kill 3, wound 8 in southern Iran: Iranian state media"</x:v>
       </x:c>
       <x:c r="W44" t="str">
-        <x:v>Xinhua News Agency</x:v>
+        <x:v>Agence France Presse</x:v>
       </x:c>
       <x:c r="X44" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-18</x:v>
       </x:c>
       <x:c r="Y44" t="str">
-        <x:v>1 killed, several wounded in U.S. overnight strikes on 2 provinces in Iran</x:v>
+        <x:v>US strikes kill 3, wound 8 in southern Iran: Iranian state media</x:v>
       </x:c>
       <x:c r="Z44" t="str">
-        <x:v>semi-official Fars news agency</x:v>
+        <x:v>deputy political, security and social affairs governor of Hormozgan</x:v>
       </x:c>
       <x:c r="AA44" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AB44" t="str">
-        <x:v>Tabriz town</x:v>
+        <x:v>Hormozgan province</x:v>
       </x:c>
       <x:c r="AC44" t="str">
-        <x:v>military area southwest of the provincial capital Tabriz</x:v>
+        <x:v>Hormozgan province</x:v>
       </x:c>
       <x:c r="AD44" t="str">
-        <x:v>East Azarbaijan province</x:v>
-      </x:c>
-      <x:c r="AE44" t="str">
-        <x:v>Tabriz county</x:v>
-      </x:c>
+        <x:v>Hormozgan province</x:v>
+      </x:c>
+      <x:c r="AE44"/>
       <x:c r="AF44" t="n">
-        <x:v>38.080256</x:v>
+        <x:v>27.1884</x:v>
       </x:c>
       <x:c r="AG44" t="n">
-        <x:v>46.292389</x:v>
+        <x:v>56.2768</x:v>
       </x:c>
       <x:c r="AH44" t="str">
-        <x:v>POINT (46.292389 38.080256)</x:v>
+        <x:v>POINT (56.2768 27.1884)</x:v>
       </x:c>
       <x:c r="AI44" t="n">
-        <x:v>184773</x:v>
+        <x:v>168953</x:v>
       </x:c>
       <x:c r="AJ44" t="str">
         <x:v>Iran</x:v>
@@ -7439,11 +7465,11 @@
       <x:c r="AN44" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO44" s="34" t="d">
-        <x:v>2026-07-20T00:00:00.000Z</x:v>
+      <x:c r="AO44" s="36" t="d">
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP44" s="30" t="d">
-        <x:v>2026-07-20T00:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ44" t="n">
         <x:v>0</x:v>
@@ -7455,16 +7481,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT44" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AU44" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AV44" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AW44" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AX44" t="n">
         <x:v>630</x:v>
@@ -7479,13 +7505,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B45" s="18" t="str">
-        <x:v>US launches new strikes as Iran warns of regional turmoil</x:v>
+        <x:v>1 killed, several wounded in U.S. overnight strikes on 2 provinces in Iran</x:v>
       </x:c>
       <x:c r="C45" t="n">
-        <x:v>637743</x:v>
+        <x:v>637525</x:v>
       </x:c>
       <x:c r="D45" t="str">
-        <x:v>IRN-2026-1-18868-137</x:v>
+        <x:v>IRN-2026-1-18868-121</x:v>
       </x:c>
       <x:c r="E45" t="n">
         <x:v>2026</x:v>
@@ -7537,46 +7563,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V45" t="str">
-        <x:v>"Al Jazeera English,2026-07-22,US launches new strikes as Iran warns of regional turmoil"</x:v>
+        <x:v>"Xinhua News Agency,2026-07-20,1 killed, several wounded in U.S. overnight strikes on 2 provinces in Iran"</x:v>
       </x:c>
       <x:c r="W45" t="str">
-        <x:v>Al Jazeera English</x:v>
+        <x:v>Xinhua News Agency</x:v>
       </x:c>
       <x:c r="X45" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="Y45" t="str">
-        <x:v>US launches new strikes as Iran warns of regional turmoil</x:v>
+        <x:v>1 killed, several wounded in U.S. overnight strikes on 2 provinces in Iran</x:v>
       </x:c>
       <x:c r="Z45" t="str">
-        <x:v>Iranian media</x:v>
+        <x:v>semi-official Fars news agency</x:v>
       </x:c>
       <x:c r="AA45" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB45" t="str">
-        <x:v>Shalamcheh border crossing</x:v>
+        <x:v>Tabriz town</x:v>
       </x:c>
       <x:c r="AC45" t="str">
-        <x:v>Shalamcheh border crossing between Iran and Iraq</x:v>
+        <x:v>military area southwest of the provincial capital Tabriz</x:v>
       </x:c>
       <x:c r="AD45" t="str">
-        <x:v>Khuzestan province</x:v>
+        <x:v>East Azarbaijan province</x:v>
       </x:c>
       <x:c r="AE45" t="str">
-        <x:v>Khorramshahr county</x:v>
+        <x:v>Tabriz county</x:v>
       </x:c>
       <x:c r="AF45" t="n">
-        <x:v>30.50526</x:v>
+        <x:v>38.080256</x:v>
       </x:c>
       <x:c r="AG45" t="n">
-        <x:v>48.02656</x:v>
+        <x:v>46.292389</x:v>
       </x:c>
       <x:c r="AH45" t="str">
-        <x:v>POINT (48.02656 30.50526)</x:v>
+        <x:v>POINT (46.292389 38.080256)</x:v>
       </x:c>
       <x:c r="AI45" t="n">
-        <x:v>173977</x:v>
+        <x:v>184773</x:v>
       </x:c>
       <x:c r="AJ45" t="str">
         <x:v>Iran</x:v>
@@ -7593,11 +7619,11 @@
       <x:c r="AN45" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO45" s="34" t="d">
-        <x:v>2026-07-22T00:00:00.000Z</x:v>
+      <x:c r="AO45" s="36" t="d">
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP45" s="30" t="d">
-        <x:v>2026-07-22T00:00:00.000Z</x:v>
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ45" t="n">
         <x:v>0</x:v>
@@ -7609,16 +7635,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT45" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AU45" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AV45" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AW45" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AX45" t="n">
         <x:v>630</x:v>
@@ -7633,13 +7659,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B46" s="18" t="str">
-        <x:v>Iran says US attack on southwest kills at least four people</x:v>
+        <x:v>US launches new strikes as Iran warns of regional turmoil</x:v>
       </x:c>
       <x:c r="C46" t="n">
-        <x:v>637553</x:v>
+        <x:v>637743</x:v>
       </x:c>
       <x:c r="D46" t="str">
-        <x:v>IRN-2026-1-18868-131</x:v>
+        <x:v>IRN-2026-1-18868-137</x:v>
       </x:c>
       <x:c r="E46" t="n">
         <x:v>2026</x:v>
@@ -7691,46 +7717,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V46" t="str">
-        <x:v>"Agence France Presse,2026-07-24,Iran says US attack on southwest kills at least four people"</x:v>
+        <x:v>"Al Jazeera English,2026-07-22,US launches new strikes as Iran warns of regional turmoil"</x:v>
       </x:c>
       <x:c r="W46" t="str">
-        <x:v>Agence France Presse</x:v>
+        <x:v>Al Jazeera English</x:v>
       </x:c>
       <x:c r="X46" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="Y46" t="str">
-        <x:v>Iran says US attack on southwest kills at least four people</x:v>
+        <x:v>US launches new strikes as Iran warns of regional turmoil</x:v>
       </x:c>
       <x:c r="Z46" t="str">
-        <x:v>deputy governor of Khuzestan province</x:v>
+        <x:v>Iranian media</x:v>
       </x:c>
       <x:c r="AA46" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AB46" t="str">
-        <x:v>Ahvaz town</x:v>
+        <x:v>Shalamcheh border crossing</x:v>
       </x:c>
       <x:c r="AC46" t="str">
-        <x:v>around the city of Ahvaz</x:v>
+        <x:v>Shalamcheh border crossing between Iran and Iraq</x:v>
       </x:c>
       <x:c r="AD46" t="str">
         <x:v>Khuzestan province</x:v>
       </x:c>
       <x:c r="AE46" t="str">
-        <x:v>Ahvaz county</x:v>
+        <x:v>Khorramshahr county</x:v>
       </x:c>
       <x:c r="AF46" t="n">
-        <x:v>31.320278</x:v>
+        <x:v>30.50526</x:v>
       </x:c>
       <x:c r="AG46" t="n">
-        <x:v>48.669167</x:v>
+        <x:v>48.02656</x:v>
       </x:c>
       <x:c r="AH46" t="str">
-        <x:v>POINT (48.669167 31.320278)</x:v>
+        <x:v>POINT (48.02656 30.50526)</x:v>
       </x:c>
       <x:c r="AI46" t="n">
-        <x:v>174698</x:v>
+        <x:v>173977</x:v>
       </x:c>
       <x:c r="AJ46" t="str">
         <x:v>Iran</x:v>
@@ -7747,11 +7773,11 @@
       <x:c r="AN46" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO46" s="34" t="d">
-        <x:v>2026-07-24T00:00:00.000Z</x:v>
+      <x:c r="AO46" s="36" t="d">
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP46" s="30" t="d">
-        <x:v>2026-07-24T00:00:00.000Z</x:v>
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ46" t="n">
         <x:v>0</x:v>
@@ -7763,16 +7789,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AT46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AU46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AV46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AW46" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AX46" t="n">
         <x:v>630</x:v>
@@ -7787,13 +7813,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B47" s="18" t="str">
-        <x:v>US strike kills three in Qeshm: Iranian media</x:v>
+        <x:v>Iran says US attack on southwest kills at least four people</x:v>
       </x:c>
       <x:c r="C47" t="n">
-        <x:v>637563</x:v>
+        <x:v>637553</x:v>
       </x:c>
       <x:c r="D47" t="str">
-        <x:v>IRN-2026-1-18868-134</x:v>
+        <x:v>IRN-2026-1-18868-131</x:v>
       </x:c>
       <x:c r="E47" t="n">
         <x:v>2026</x:v>
@@ -7845,46 +7871,46 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V47" t="str">
-        <x:v>"Agence France Presse,2026-07-30,US strike kills three in Qeshm: Iranian media"</x:v>
+        <x:v>"Agence France Presse,2026-07-24,Iran says US attack on southwest kills at least four people"</x:v>
       </x:c>
       <x:c r="W47" t="str">
         <x:v>Agence France Presse</x:v>
       </x:c>
       <x:c r="X47" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
       <x:c r="Y47" t="str">
-        <x:v>US strike kills three in Qeshm: Iranian media</x:v>
+        <x:v>Iran says US attack on southwest kills at least four people</x:v>
       </x:c>
       <x:c r="Z47" t="str">
-        <x:v>Hormozgan University of Medical Sciences</x:v>
+        <x:v>deputy governor of Khuzestan province</x:v>
       </x:c>
       <x:c r="AA47" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AB47" t="str">
-        <x:v>Qeshm town</x:v>
+        <x:v>Ahvaz town</x:v>
       </x:c>
       <x:c r="AC47" t="str">
-        <x:v>Chah Tangu neighbourhood of Qeshm</x:v>
+        <x:v>around the city of Ahvaz</x:v>
       </x:c>
       <x:c r="AD47" t="str">
-        <x:v>Hormozgan province</x:v>
+        <x:v>Khuzestan province</x:v>
       </x:c>
       <x:c r="AE47" t="str">
-        <x:v>Qeshm county</x:v>
+        <x:v>Ahvaz county</x:v>
       </x:c>
       <x:c r="AF47" t="n">
-        <x:v>26.9492</x:v>
+        <x:v>31.320278</x:v>
       </x:c>
       <x:c r="AG47" t="n">
-        <x:v>56.2691</x:v>
+        <x:v>48.669167</x:v>
       </x:c>
       <x:c r="AH47" t="str">
-        <x:v>POINT (56.2691 26.9492)</x:v>
+        <x:v>POINT (48.669167 31.320278)</x:v>
       </x:c>
       <x:c r="AI47" t="n">
-        <x:v>168233</x:v>
+        <x:v>174698</x:v>
       </x:c>
       <x:c r="AJ47" t="str">
         <x:v>Iran</x:v>
@@ -7901,11 +7927,11 @@
       <x:c r="AN47" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO47" s="35" t="d">
-        <x:v>2026-07-30T00:00:00.000Z</x:v>
+      <x:c r="AO47" s="36" t="d">
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP47" s="30" t="d">
-        <x:v>2026-07-30T00:00:00.000Z</x:v>
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ47" t="n">
         <x:v>0</x:v>
@@ -7914,19 +7940,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="AS47" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="AT47" t="n">
-        <x:v>0</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AU47" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AV47" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AW47" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AX47" t="n">
         <x:v>630</x:v>
@@ -7941,13 +7967,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B48" s="18" t="str">
-        <x:v>Iran's Guards say three members killed in US attack on northwest</x:v>
+        <x:v>US strike kills three in Qeshm: Iranian media</x:v>
       </x:c>
       <x:c r="C48" t="n">
-        <x:v>637567</x:v>
+        <x:v>637563</x:v>
       </x:c>
       <x:c r="D48" t="str">
-        <x:v>IRN-2026-1-18868-136</x:v>
+        <x:v>IRN-2026-1-18868-134</x:v>
       </x:c>
       <x:c r="E48" t="n">
         <x:v>2026</x:v>
@@ -7999,7 +8025,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V48" t="str">
-        <x:v>"Agence France Presse,2026-07-30,Iran's Guards say three members killed in US attack on northwest"</x:v>
+        <x:v>"Agence France Presse,2026-07-30,US strike kills three in Qeshm: Iranian media"</x:v>
       </x:c>
       <x:c r="W48" t="str">
         <x:v>Agence France Presse</x:v>
@@ -8008,35 +8034,37 @@
         <x:v>2026-07-30</x:v>
       </x:c>
       <x:c r="Y48" t="str">
-        <x:v>Iran's Guards say three members killed in US attack on northwest</x:v>
+        <x:v>US strike kills three in Qeshm: Iranian media</x:v>
       </x:c>
       <x:c r="Z48" t="str">
-        <x:v>IRGC</x:v>
+        <x:v>Hormozgan University of Medical Sciences</x:v>
       </x:c>
       <x:c r="AA48" t="n">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="AB48" t="str">
-        <x:v>Zanjan province</x:v>
+        <x:v>Qeshm town</x:v>
       </x:c>
       <x:c r="AC48" t="str">
-        <x:v>Zanjan province</x:v>
+        <x:v>Chah Tangu neighbourhood of Qeshm</x:v>
       </x:c>
       <x:c r="AD48" t="str">
-        <x:v>Zanjan province</x:v>
-      </x:c>
-      <x:c r="AE48"/>
+        <x:v>Hormozgan province</x:v>
+      </x:c>
+      <x:c r="AE48" t="str">
+        <x:v>Qeshm county</x:v>
+      </x:c>
       <x:c r="AF48" t="n">
-        <x:v>36.6751</x:v>
+        <x:v>26.9492</x:v>
       </x:c>
       <x:c r="AG48" t="n">
-        <x:v>48.4845</x:v>
+        <x:v>56.2691</x:v>
       </x:c>
       <x:c r="AH48" t="str">
-        <x:v>POINT (48.4845 36.6751)</x:v>
+        <x:v>POINT (56.2691 26.9492)</x:v>
       </x:c>
       <x:c r="AI48" t="n">
-        <x:v>182617</x:v>
+        <x:v>168233</x:v>
       </x:c>
       <x:c r="AJ48" t="str">
         <x:v>Iran</x:v>
@@ -8053,20 +8081,20 @@
       <x:c r="AN48" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AO48" s="35" t="d">
+      <x:c r="AO48" s="37" t="d">
         <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AP48" s="30" t="d">
         <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="AQ48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AR48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS48" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="AR48" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS48" t="n">
-        <x:v>0</x:v>
       </x:c>
       <x:c r="AT48" t="n">
         <x:v>0</x:v>
@@ -8093,14 +8121,13 @@
         <x:v>US</x:v>
       </x:c>
       <x:c r="B49" s="18" t="str">
-        <x:v>Urgent: Iran's IRGC says several killed, wounded in U.S. attack on Larak island, vows
-"response and punishment"</x:v>
+        <x:v>Iran's Guards say three members killed in US attack on northwest</x:v>
       </x:c>
       <x:c r="C49" t="n">
-        <x:v>640608</x:v>
+        <x:v>637567</x:v>
       </x:c>
       <x:c r="D49" t="str">
-        <x:v>IRN-2026-1-18868-344</x:v>
+        <x:v>IRN-2026-1-18868-136</x:v>
       </x:c>
       <x:c r="E49" t="n">
         <x:v>2026</x:v>
@@ -8109,7 +8136,7 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="G49" t="str">
-        <x:v>Check geography</x:v>
+        <x:v>Clear</x:v>
       </x:c>
       <x:c r="H49" t="n">
         <x:v>1</x:v>
@@ -8149,106 +8176,259 @@
         <x:v>Government of Israel, Government of United States of America</x:v>
       </x:c>
       <x:c r="U49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="V49" t="str">
+        <x:v>"Agence France Presse,2026-07-30,Iran's Guards say three members killed in US attack on northwest"</x:v>
+      </x:c>
+      <x:c r="W49" t="str">
+        <x:v>Agence France Presse</x:v>
+      </x:c>
+      <x:c r="X49" t="str">
+        <x:v>2026-07-30</x:v>
+      </x:c>
+      <x:c r="Y49" t="str">
+        <x:v>Iran's Guards say three members killed in US attack on northwest</x:v>
+      </x:c>
+      <x:c r="Z49" t="str">
+        <x:v>IRGC</x:v>
+      </x:c>
+      <x:c r="AA49" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AB49" t="str">
+        <x:v>Zanjan province</x:v>
+      </x:c>
+      <x:c r="AC49" t="str">
+        <x:v>Zanjan province</x:v>
+      </x:c>
+      <x:c r="AD49" t="str">
+        <x:v>Zanjan province</x:v>
+      </x:c>
+      <x:c r="AE49"/>
+      <x:c r="AF49" t="n">
+        <x:v>36.6751</x:v>
+      </x:c>
+      <x:c r="AG49" t="n">
+        <x:v>48.4845</x:v>
+      </x:c>
+      <x:c r="AH49" t="str">
+        <x:v>POINT (48.4845 36.6751)</x:v>
+      </x:c>
+      <x:c r="AI49" t="n">
+        <x:v>182617</x:v>
+      </x:c>
+      <x:c r="AJ49" t="str">
+        <x:v>Iran</x:v>
+      </x:c>
+      <x:c r="AK49" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="AL49" t="str">
+        <x:v>Middle East</x:v>
+      </x:c>
+      <x:c r="AM49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO49" s="37" t="d">
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="AP49" s="30" t="d">
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="AQ49" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AR49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AT49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AU49" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AV49" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AW49" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AX49" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="AY49"/>
+      <x:c r="AZ49" t="str">
+        <x:v>26.0.7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="18" t="str">
+        <x:v>US</x:v>
+      </x:c>
+      <x:c r="B50" s="18" t="str">
+        <x:v>Urgent: Iran's IRGC says several killed, wounded in U.S. attack on Larak island, vows
+"response and punishment"</x:v>
+      </x:c>
+      <x:c r="C50" t="n">
+        <x:v>640608</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>IRN-2026-1-18868-344</x:v>
+      </x:c>
+      <x:c r="E50" t="n">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="G50" t="str">
+        <x:v>Check geography</x:v>
+      </x:c>
+      <x:c r="H50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I50"/>
+      <x:c r="J50" t="n">
+        <x:v>16905</x:v>
+      </x:c>
+      <x:c r="K50" t="str">
+        <x:v>Iran - Israel, United States of America</x:v>
+      </x:c>
+      <x:c r="L50" t="n">
+        <x:v>18868</x:v>
+      </x:c>
+      <x:c r="M50" t="n">
+        <x:v>18868</x:v>
+      </x:c>
+      <x:c r="N50" t="str">
+        <x:v>Government of Iran - Government of Israel, Government of United States of America</x:v>
+      </x:c>
+      <x:c r="O50" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="P50" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="Q50" t="str">
+        <x:v>Government of Iran</x:v>
+      </x:c>
+      <x:c r="R50" t="n">
+        <x:v>9865</x:v>
+      </x:c>
+      <x:c r="S50" t="n">
+        <x:v>9865</x:v>
+      </x:c>
+      <x:c r="T50" t="str">
+        <x:v>Government of Israel, Government of United States of America</x:v>
+      </x:c>
+      <x:c r="U50" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="V49" t="str">
+      <x:c r="V50" t="str">
         <x:v>"Xinhua News Agency,2026-08-30,Urgent: Iran's IRGC says several killed, wounded in U.S. attack on Larak island, vows
 "response and punishment"";"Xinhua News Agency,2026-08-30,1st LD Writethru: Iran's IRGC says several killed, wounded in U.S. attack on Larak Island,
 vows "punishment""</x:v>
       </x:c>
-      <x:c r="W49" t="str">
+      <x:c r="W50" t="str">
         <x:v>Xinhua News Agency;Xinhua News Agency</x:v>
       </x:c>
-      <x:c r="X49" t="str">
+      <x:c r="X50" t="str">
         <x:v>2026-08-30;2026-08-30</x:v>
       </x:c>
-      <x:c r="Y49" t="str">
+      <x:c r="Y50" t="str">
         <x:v>Urgent: Iran's IRGC says several killed, wounded in U.S. attack on Larak island, vows
 "response and punishment";1st LD Writethru: Iran's IRGC says several killed, wounded in U.S. attack on Larak Island,
 vows "punishment"</x:v>
       </x:c>
-      <x:c r="Z49" t="str">
+      <x:c r="Z50" t="str">
         <x:v>IRGC</x:v>
       </x:c>
-      <x:c r="AA49" t="n">
+      <x:c r="AA50" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AB49" t="str">
+      <x:c r="AB50" t="str">
         <x:v>Hormozgan province</x:v>
       </x:c>
-      <x:c r="AC49" t="str">
+      <x:c r="AC50" t="str">
         <x:v>Larak Island in Hormozgan province</x:v>
       </x:c>
-      <x:c r="AD49" t="str">
+      <x:c r="AD50" t="str">
         <x:v>Hormozgan province</x:v>
       </x:c>
-      <x:c r="AE49"/>
-      <x:c r="AF49" t="n">
+      <x:c r="AE50"/>
+      <x:c r="AF50" t="n">
         <x:v>27.1884</x:v>
       </x:c>
-      <x:c r="AG49" t="n">
+      <x:c r="AG50" t="n">
         <x:v>56.2768</x:v>
       </x:c>
-      <x:c r="AH49" t="str">
+      <x:c r="AH50" t="str">
         <x:v>POINT (56.2768 27.1884)</x:v>
       </x:c>
-      <x:c r="AI49" t="n">
+      <x:c r="AI50" t="n">
         <x:v>168953</x:v>
       </x:c>
-      <x:c r="AJ49" t="str">
+      <x:c r="AJ50" t="str">
         <x:v>Iran</x:v>
       </x:c>
-      <x:c r="AK49" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="AL49" t="str">
+      <x:c r="AK50" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="AL50" t="str">
         <x:v>Middle East</x:v>
       </x:c>
-      <x:c r="AM49" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AN49" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="AO49" s="36" t="d">
+      <x:c r="AM50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AN50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO50" s="38" t="d">
         <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="AP49" s="30" t="d">
+      <x:c r="AP50" s="30" t="d">
         <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="AQ49" t="n">
+      <x:c r="AQ50" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AR49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AS49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AT49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="AU49" t="n">
+      <x:c r="AR50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AS50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AT50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AU50" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AV49" t="n">
+      <x:c r="AV50" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="AW49" t="n">
+      <x:c r="AW50" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AX49" t="n">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="AY49"/>
-      <x:c r="AZ49" t="str">
+      <x:c r="AX50" t="n">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="AY50"/>
+      <x:c r="AZ50" t="str">
         <x:v>26.0.8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3b9639f81f24c74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27a0937d199046af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8271,766 +8451,766 @@
   </x:cols>
   <x:sheetData>
     <x:row r="2">
-      <x:c r="A2" s="42" t="str">
+      <x:c r="A2" s="43" t="str">
         <x:v>Original and refreshed dates</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="44" customHeight="1">
-      <x:c r="A5" s="47" t="str">
+      <x:c r="A5" s="48" t="str">
         <x:v>Start date</x:v>
       </x:c>
-      <x:c r="B5" s="47" t="str">
+      <x:c r="B5" s="48" t="str">
         <x:v>UCDP records</x:v>
       </x:c>
-      <x:c r="C5" s="47" t="str">
+      <x:c r="C5" s="48" t="str">
         <x:v>Event IDs</x:v>
       </x:c>
-      <x:c r="D5" s="47" t="str">
+      <x:c r="D5" s="48" t="str">
         <x:v>Original selection</x:v>
       </x:c>
-      <x:c r="E5" s="47" t="str">
+      <x:c r="E5" s="48" t="str">
         <x:v>Current timeline</x:v>
       </x:c>
-      <x:c r="F5" s="47" t="str">
+      <x:c r="F5" s="48" t="str">
         <x:v>Original matched posts</x:v>
       </x:c>
-      <x:c r="G5" s="47" t="str">
+      <x:c r="G5" s="48" t="str">
         <x:v>Current matched posts</x:v>
       </x:c>
-      <x:c r="H5" s="47" t="str">
+      <x:c r="H5" s="48" t="str">
         <x:v>Date status</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="35" customHeight="1">
-      <x:c r="A6" s="49" t="d">
+      <x:c r="A6" s="50" t="d">
         <x:v>2026-02-28T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B6" s="50" t="n">
+      <x:c r="B6" s="51" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C6" s="51" t="str">
+      <x:c r="C6" s="52" t="str">
         <x:v>620876, 620877, 621091, 625182, 625367, 625374, 629399</x:v>
       </x:c>
-      <x:c r="D6" s="50" t="str">
+      <x:c r="D6" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E6" s="50" t="str">
+      <x:c r="E6" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F6" s="50" t="n">
+      <x:c r="F6" s="51" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G6" s="50" t="n">
+      <x:c r="G6" s="51" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H6" s="51" t="str">
+      <x:c r="H6" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="35" customHeight="1">
-      <x:c r="A7" s="49" t="d">
+      <x:c r="A7" s="50" t="d">
         <x:v>2026-03-04T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B7" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="51" t="str">
+      <x:c r="B7" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="52" t="str">
         <x:v>625183</x:v>
       </x:c>
-      <x:c r="D7" s="50" t="str">
+      <x:c r="D7" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E7" s="50" t="str">
+      <x:c r="E7" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F7" s="50" t="n">
+      <x:c r="F7" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="50" t="n">
+      <x:c r="G7" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="51" t="str">
+      <x:c r="H7" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="35" customHeight="1">
-      <x:c r="A8" s="49" t="d">
+      <x:c r="A8" s="50" t="d">
         <x:v>2026-03-08T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B8" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="51" t="str">
+      <x:c r="B8" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="52" t="str">
         <x:v>625187</x:v>
       </x:c>
-      <x:c r="D8" s="50" t="str">
+      <x:c r="D8" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E8" s="50" t="str">
+      <x:c r="E8" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F8" s="50" t="n">
+      <x:c r="F8" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G8" s="50" t="n">
+      <x:c r="G8" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H8" s="51" t="str">
+      <x:c r="H8" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="35" customHeight="1">
-      <x:c r="A9" s="49" t="d">
+      <x:c r="A9" s="50" t="d">
         <x:v>2026-03-20T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B9" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="51" t="str">
+      <x:c r="B9" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="52" t="str">
         <x:v>625358</x:v>
       </x:c>
-      <x:c r="D9" s="50" t="str">
+      <x:c r="D9" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E9" s="50" t="str">
+      <x:c r="E9" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F9" s="50" t="n">
+      <x:c r="F9" s="51" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G9" s="50" t="n">
+      <x:c r="G9" s="51" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H9" s="51" t="str">
+      <x:c r="H9" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="35" customHeight="1">
-      <x:c r="A10" s="49" t="d">
+      <x:c r="A10" s="50" t="d">
         <x:v>2026-03-27T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B10" s="50" t="n">
+      <x:c r="B10" s="51" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C10" s="51" t="str">
+      <x:c r="C10" s="52" t="str">
         <x:v>625363, 625364</x:v>
       </x:c>
-      <x:c r="D10" s="50" t="str">
+      <x:c r="D10" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E10" s="50" t="str">
+      <x:c r="E10" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F10" s="50" t="n">
+      <x:c r="F10" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G10" s="50" t="n">
+      <x:c r="G10" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H10" s="51" t="str">
+      <x:c r="H10" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="35" customHeight="1">
-      <x:c r="A11" s="49" t="d">
+      <x:c r="A11" s="50" t="d">
         <x:v>2026-03-29T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B11" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="51" t="str">
+      <x:c r="B11" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="52" t="str">
         <x:v>625366</x:v>
       </x:c>
-      <x:c r="D11" s="50" t="str">
+      <x:c r="D11" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E11" s="50" t="str">
+      <x:c r="E11" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F11" s="50" t="n">
+      <x:c r="F11" s="51" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G11" s="50" t="n">
+      <x:c r="G11" s="51" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H11" s="51" t="str">
+      <x:c r="H11" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="35" customHeight="1">
-      <x:c r="A12" s="49" t="d">
+      <x:c r="A12" s="50" t="d">
         <x:v>2026-03-30T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B12" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="51" t="str">
+      <x:c r="B12" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="52" t="str">
         <x:v>625369</x:v>
       </x:c>
-      <x:c r="D12" s="50" t="str">
+      <x:c r="D12" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E12" s="50" t="str">
+      <x:c r="E12" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F12" s="50" t="n">
+      <x:c r="F12" s="51" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G12" s="50" t="n">
+      <x:c r="G12" s="51" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H12" s="51" t="str">
+      <x:c r="H12" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="35" customHeight="1">
-      <x:c r="A13" s="49" t="d">
+      <x:c r="A13" s="50" t="d">
         <x:v>2026-03-31T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B13" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="51" t="str">
+      <x:c r="B13" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="52" t="str">
         <x:v>625368</x:v>
       </x:c>
-      <x:c r="D13" s="50" t="str">
+      <x:c r="D13" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E13" s="50" t="str">
+      <x:c r="E13" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F13" s="50" t="n">
+      <x:c r="F13" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G13" s="50" t="n">
+      <x:c r="G13" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H13" s="51" t="str">
+      <x:c r="H13" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="35" customHeight="1">
-      <x:c r="A14" s="49" t="d">
+      <x:c r="A14" s="50" t="d">
         <x:v>2026-04-02T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B14" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C14" s="51" t="str">
+      <x:c r="B14" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C14" s="52" t="str">
         <x:v>625373</x:v>
       </x:c>
-      <x:c r="D14" s="50" t="str">
+      <x:c r="D14" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E14" s="50" t="str">
+      <x:c r="E14" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F14" s="50" t="n">
+      <x:c r="F14" s="51" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G14" s="50" t="n">
+      <x:c r="G14" s="51" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H14" s="51" t="str">
+      <x:c r="H14" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="35" customHeight="1">
-      <x:c r="A15" s="49" t="d">
+      <x:c r="A15" s="50" t="d">
         <x:v>2026-04-04T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B15" s="50" t="n">
+      <x:c r="B15" s="51" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C15" s="51" t="str">
+      <x:c r="C15" s="52" t="str">
         <x:v>628242, 629298, 629314</x:v>
       </x:c>
-      <x:c r="D15" s="50" t="str">
+      <x:c r="D15" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E15" s="50" t="str">
+      <x:c r="E15" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F15" s="50" t="n">
+      <x:c r="F15" s="51" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="G15" s="50" t="n">
+      <x:c r="G15" s="51" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H15" s="51" t="str">
+      <x:c r="H15" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="35" customHeight="1">
-      <x:c r="A16" s="49" t="d">
+      <x:c r="A16" s="50" t="d">
         <x:v>2026-04-05T00:00:00.000Z</x:v>
       </x:c>
-      <x:c r="B16" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="51" t="str">
-        <x:v>629302</x:v>
-      </x:c>
-      <x:c r="D16" s="50" t="str">
+      <x:c r="B16" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C16" s="52" t="str">
+        <x:v>629301, 629302</x:v>
+      </x:c>
+      <x:c r="D16" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E16" s="50" t="str">
+      <x:c r="E16" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F16" s="50" t="n">
+      <x:c r="F16" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G16" s="50" t="n">
+      <x:c r="G16" s="51" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H16" s="51" t="str">
+      <x:c r="H16" s="52" t="str">
+        <x:v>Original date; rescue record added</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="35" customHeight="1">
+      <x:c r="A17" s="50" t="d">
+        <x:v>2026-04-06T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B17" s="51" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C17" s="52" t="str">
+        <x:v>629305, 629306, 629307, 629308</x:v>
+      </x:c>
+      <x:c r="D17" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E17" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F17" s="51" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="G17" s="51" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="H17" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="35" customHeight="1">
-      <x:c r="A17" s="49" t="d">
-        <x:v>2026-04-06T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B17" s="50" t="n">
+    <x:row r="18" ht="35" customHeight="1">
+      <x:c r="A18" s="50" t="d">
+        <x:v>2026-04-07T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B18" s="51" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C18" s="52" t="str">
+        <x:v>629311, 629312, 629313</x:v>
+      </x:c>
+      <x:c r="D18" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E18" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F18" s="51" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G18" s="51" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H18" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="35" customHeight="1">
+      <x:c r="A19" s="50" t="d">
+        <x:v>2026-05-04T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B19" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C19" s="52" t="str">
+        <x:v>629402</x:v>
+      </x:c>
+      <x:c r="D19" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E19" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F19" s="51" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G19" s="51" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H19" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="35" customHeight="1">
+      <x:c r="A20" s="50" t="d">
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B20" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C20" s="52" t="str">
+        <x:v>637547</x:v>
+      </x:c>
+      <x:c r="D20" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E20" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F20" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G20" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H20" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="35" customHeight="1">
+      <x:c r="A21" s="50" t="d">
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B21" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C21" s="52" t="str">
+        <x:v>637517, 637518, 637519, 637521, 637534</x:v>
+      </x:c>
+      <x:c r="D21" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E21" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F21" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G21" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H21" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="35" customHeight="1">
+      <x:c r="A22" s="50" t="d">
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B22" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C22" s="52" t="str">
+        <x:v>637520</x:v>
+      </x:c>
+      <x:c r="D22" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E22" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F22" s="51" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G22" s="51" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H22" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="35" customHeight="1">
+      <x:c r="A23" s="50" t="d">
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B23" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C23" s="52" t="str">
+        <x:v>637523</x:v>
+      </x:c>
+      <x:c r="D23" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E23" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F23" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G23" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H23" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="35" customHeight="1">
+      <x:c r="A24" s="50" t="d">
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B24" s="51" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C24" s="52" t="str">
+        <x:v>637526, 637528</x:v>
+      </x:c>
+      <x:c r="D24" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E24" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F24" s="51" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C17" s="51" t="str">
-        <x:v>629305, 629306, 629307, 629308</x:v>
-      </x:c>
-      <x:c r="D17" s="50" t="str">
+      <x:c r="G24" s="51" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H24" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="35" customHeight="1">
+      <x:c r="A25" s="50" t="d">
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B25" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C25" s="52" t="str">
+        <x:v>637532</x:v>
+      </x:c>
+      <x:c r="D25" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="E17" s="50" t="str">
+      <x:c r="E25" s="51" t="str">
         <x:v>Yes</x:v>
       </x:c>
-      <x:c r="F17" s="50" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="G17" s="50" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="H17" s="51" t="str">
+      <x:c r="F25" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G25" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H25" s="52" t="str">
         <x:v>Original selected date</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="35" customHeight="1">
-      <x:c r="A18" s="49" t="d">
-        <x:v>2026-04-07T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B18" s="50" t="n">
+    <x:row r="26" ht="35" customHeight="1">
+      <x:c r="A26" s="50" t="d">
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B26" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C26" s="52" t="str">
+        <x:v>637540</x:v>
+      </x:c>
+      <x:c r="D26" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E26" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F26" s="51" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G26" s="51" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H26" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="35" customHeight="1">
+      <x:c r="A27" s="50" t="d">
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B27" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C27" s="52" t="str">
+        <x:v>637542</x:v>
+      </x:c>
+      <x:c r="D27" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E27" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F27" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G27" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="35" customHeight="1">
+      <x:c r="A28" s="50" t="d">
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B28" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C28" s="52" t="str">
+        <x:v>637545</x:v>
+      </x:c>
+      <x:c r="D28" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E28" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F28" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G28" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H28" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="35" customHeight="1">
+      <x:c r="A29" s="50" t="d">
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B29" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C29" s="52" t="str">
+        <x:v>637525</x:v>
+      </x:c>
+      <x:c r="D29" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E29" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F29" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G29" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H29" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="35" customHeight="1">
+      <x:c r="A30" s="50" t="d">
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B30" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C30" s="52" t="str">
+        <x:v>637743</x:v>
+      </x:c>
+      <x:c r="D30" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E30" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F30" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G30" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H30" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="35" customHeight="1">
+      <x:c r="A31" s="50" t="d">
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B31" s="51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C31" s="52" t="str">
+        <x:v>637553</x:v>
+      </x:c>
+      <x:c r="D31" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E31" s="51" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F31" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G31" s="51" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H31" s="52" t="str">
+        <x:v>Original selected date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="35" customHeight="1">
+      <x:c r="A32" s="53" t="d">
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B32" s="54" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C32" s="55" t="str">
+        <x:v>637563, 637567</x:v>
+      </x:c>
+      <x:c r="D32" s="54" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E32" s="54" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F32" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="55" t="str">
+        <x:v>Restored with no matched posts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="35" customHeight="1">
+      <x:c r="A33" s="56" t="d">
+        <x:v>2026-08-30T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B33" s="57" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C33" s="58" t="str">
+        <x:v>640608</x:v>
+      </x:c>
+      <x:c r="D33" s="57" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E33" s="57" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F33" s="57" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G33" s="57" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C18" s="51" t="str">
-        <x:v>629311, 629312, 629313</x:v>
-      </x:c>
-      <x:c r="D18" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E18" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F18" s="50" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G18" s="50" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H18" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="35" customHeight="1">
-      <x:c r="A19" s="49" t="d">
-        <x:v>2026-05-04T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B19" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="51" t="str">
-        <x:v>629402</x:v>
-      </x:c>
-      <x:c r="D19" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E19" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F19" s="50" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G19" s="50" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H19" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="35" customHeight="1">
-      <x:c r="A20" s="49" t="d">
-        <x:v>2026-06-27T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B20" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="51" t="str">
-        <x:v>637547</x:v>
-      </x:c>
-      <x:c r="D20" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E20" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F20" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G20" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H20" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="35" customHeight="1">
-      <x:c r="A21" s="49" t="d">
-        <x:v>2026-07-08T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B21" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="51" t="str">
-        <x:v>637517, 637518, 637519, 637521, 637534</x:v>
-      </x:c>
-      <x:c r="D21" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E21" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F21" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G21" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="35" customHeight="1">
-      <x:c r="A22" s="49" t="d">
-        <x:v>2026-07-09T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B22" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="51" t="str">
-        <x:v>637520</x:v>
-      </x:c>
-      <x:c r="D22" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E22" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F22" s="50" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G22" s="50" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H22" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="35" customHeight="1">
-      <x:c r="A23" s="49" t="d">
-        <x:v>2026-07-12T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B23" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="51" t="str">
-        <x:v>637523</x:v>
-      </x:c>
-      <x:c r="D23" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E23" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F23" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G23" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="35" customHeight="1">
-      <x:c r="A24" s="49" t="d">
-        <x:v>2026-07-13T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B24" s="50" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="51" t="str">
-        <x:v>637526, 637528</x:v>
-      </x:c>
-      <x:c r="D24" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E24" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F24" s="50" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G24" s="50" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H24" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="35" customHeight="1">
-      <x:c r="A25" s="49" t="d">
-        <x:v>2026-07-14T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B25" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="51" t="str">
-        <x:v>637532</x:v>
-      </x:c>
-      <x:c r="D25" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E25" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F25" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G25" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H25" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="35" customHeight="1">
-      <x:c r="A26" s="49" t="d">
-        <x:v>2026-07-15T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B26" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C26" s="51" t="str">
-        <x:v>637540</x:v>
-      </x:c>
-      <x:c r="D26" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E26" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F26" s="50" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G26" s="50" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H26" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="35" customHeight="1">
-      <x:c r="A27" s="49" t="d">
-        <x:v>2026-07-16T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B27" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C27" s="51" t="str">
-        <x:v>637542</x:v>
-      </x:c>
-      <x:c r="D27" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E27" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F27" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G27" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="35" customHeight="1">
-      <x:c r="A28" s="49" t="d">
-        <x:v>2026-07-18T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B28" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C28" s="51" t="str">
-        <x:v>637545</x:v>
-      </x:c>
-      <x:c r="D28" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E28" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F28" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G28" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H28" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="35" customHeight="1">
-      <x:c r="A29" s="49" t="d">
-        <x:v>2026-07-20T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B29" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C29" s="51" t="str">
-        <x:v>637525</x:v>
-      </x:c>
-      <x:c r="D29" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E29" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F29" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G29" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H29" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="35" customHeight="1">
-      <x:c r="A30" s="49" t="d">
-        <x:v>2026-07-22T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B30" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C30" s="51" t="str">
-        <x:v>637743</x:v>
-      </x:c>
-      <x:c r="D30" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E30" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F30" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G30" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H30" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="35" customHeight="1">
-      <x:c r="A31" s="49" t="d">
-        <x:v>2026-07-24T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B31" s="50" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C31" s="51" t="str">
-        <x:v>637553</x:v>
-      </x:c>
-      <x:c r="D31" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E31" s="50" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F31" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G31" s="50" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H31" s="51" t="str">
-        <x:v>Original selected date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="35" customHeight="1">
-      <x:c r="A32" s="52" t="d">
-        <x:v>2026-07-30T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B32" s="53" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C32" s="54" t="str">
-        <x:v>637563, 637567</x:v>
-      </x:c>
-      <x:c r="D32" s="53" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E32" s="53" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F32" s="53" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32" s="53" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="54" t="str">
-        <x:v>Restored with no matched posts</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="35" customHeight="1">
-      <x:c r="A33" s="55" t="d">
-        <x:v>2026-08-30T00:00:00.000Z</x:v>
-      </x:c>
-      <x:c r="B33" s="56" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C33" s="57" t="str">
-        <x:v>640608</x:v>
-      </x:c>
-      <x:c r="D33" s="56" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E33" s="56" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F33" s="56" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G33" s="56" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H33" s="57" t="str">
+      <x:c r="H33" s="58" t="str">
         <x:v>Added August event</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="58" t="str">
+      <x:c r="A36" s="59" t="str">
         <x:v>Post counts are within each date’s ±1-calendar-day window; adjacent dates can reuse the same post.</x:v>
       </x:c>
     </x:row>
